--- a/normalizacion_datos.xlsx
+++ b/normalizacion_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Proyectos\app_agua\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{096874D9-B3F5-43E2-8549-545AE883A99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEE9614-11F4-47F8-A29D-C47B8355B1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E2268286-99C0-4F97-A086-55F9B04399C9}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="518">
   <si>
     <t>id</t>
   </si>
@@ -1249,54 +1249,6 @@
     <t>san antonio</t>
   </si>
   <si>
-    <t>MED-0081</t>
-  </si>
-  <si>
-    <t>MED-0082</t>
-  </si>
-  <si>
-    <t>MED-0083</t>
-  </si>
-  <si>
-    <t>MED-0084</t>
-  </si>
-  <si>
-    <t>MED-0085</t>
-  </si>
-  <si>
-    <t>MED-0086</t>
-  </si>
-  <si>
-    <t>MED-0087</t>
-  </si>
-  <si>
-    <t>MED-0088</t>
-  </si>
-  <si>
-    <t>meses_adeudados</t>
-  </si>
-  <si>
-    <t>desde_periodo</t>
-  </si>
-  <si>
-    <t>Enero del 2024</t>
-  </si>
-  <si>
-    <t>Julio del 2026</t>
-  </si>
-  <si>
-    <t>Marzo del 2026</t>
-  </si>
-  <si>
-    <t>Febrero del 2026</t>
-  </si>
-  <si>
-    <t>Abril del 2026</t>
-  </si>
-  <si>
-    <t>Diciembre del 2025</t>
-  </si>
-  <si>
     <t>0999999991</t>
   </si>
   <si>
@@ -1561,86 +1513,110 @@
     <t>0999999988</t>
   </si>
   <si>
-    <t>Enero del 2026</t>
-  </si>
-  <si>
-    <t>Junio del 2026</t>
-  </si>
-  <si>
-    <t>Desde el 2024, y 7 meses del 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>12 Meses sin lectura y 7 meses del 2026</t>
-  </si>
-  <si>
-    <t>7  Meses sin lectura y 7 meses del 2026</t>
-  </si>
-  <si>
-    <t>12 meses sin lectura, deuda del 2024 y 7 meses del 2026</t>
-  </si>
-  <si>
-    <t>12 meses sin lectura y 7 meses del 2026</t>
-  </si>
-  <si>
-    <t>10 meses sin lectura, 7 meses del 2026</t>
-  </si>
-  <si>
-    <t>Deudas del 2020, Deudas del 2024 y 12 meses sin lectura</t>
-  </si>
-  <si>
-    <t>Desde Julio</t>
-  </si>
-  <si>
-    <t>7 meses sin lectura, 7 meses del 2026</t>
-  </si>
-  <si>
-    <t>2 meses sin lectura, enero del 2026</t>
-  </si>
-  <si>
-    <t>Excedentes</t>
-  </si>
-  <si>
-    <t>Desde Junio del 2026</t>
-  </si>
-  <si>
-    <t>8 Meses sin lectura, Desde Enero del 2026</t>
-  </si>
-  <si>
-    <t>Desde julio del 2026</t>
-  </si>
-  <si>
-    <t>12 Meses sin lectura</t>
-  </si>
-  <si>
-    <t>3 Meses sin lectura y Desde enero del 2026</t>
-  </si>
-  <si>
-    <t>Desde junio del 2026</t>
-  </si>
-  <si>
-    <t>Deudas del 2024, 12 Meses sin lectura y 7 meses del 2026</t>
-  </si>
-  <si>
-    <t>Desde Julio del 2026</t>
-  </si>
-  <si>
-    <t>Desde Enero del 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Mes sin Lectura, </t>
-  </si>
-  <si>
-    <t>Deudas desde el 2021</t>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>José Francisco</t>
+  </si>
+  <si>
+    <t>Acurio Gamboa</t>
+  </si>
+  <si>
+    <t>0901432518</t>
+  </si>
+  <si>
+    <t>1800000004</t>
+  </si>
+  <si>
+    <t>A22L309971</t>
+  </si>
+  <si>
+    <t>A22L310645</t>
+  </si>
+  <si>
+    <t>A19L464550</t>
+  </si>
+  <si>
+    <t>1801902642</t>
+  </si>
+  <si>
+    <t>Bertha Marlene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masaquiza Moreta </t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>Jorge Maclip</t>
+  </si>
+  <si>
+    <t>Miño Angumba</t>
+  </si>
+  <si>
+    <t>1000851699</t>
+  </si>
+  <si>
+    <t>1803157229</t>
+  </si>
+  <si>
+    <t>Franklin Guillermo</t>
+  </si>
+  <si>
+    <t>Quinquiguano Lalaleo</t>
+  </si>
+  <si>
+    <t>1208020361</t>
+  </si>
+  <si>
+    <t>1801785062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloria Magdalena </t>
+  </si>
+  <si>
+    <t>1801975853</t>
+  </si>
+  <si>
+    <t>Marianita De Jesus</t>
+  </si>
+  <si>
+    <t>Miño Moreta</t>
+  </si>
+  <si>
+    <t>Elsa Maribel</t>
+  </si>
+  <si>
+    <t>1803443116</t>
+  </si>
+  <si>
+    <t>A8255519</t>
+  </si>
+  <si>
+    <t>Andrea Carolina</t>
+  </si>
+  <si>
+    <t>A08L255519</t>
+  </si>
+  <si>
+    <t>A22L310039</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>multas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1667,31 +1643,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1706,69 +1672,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="17" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2259,4027 +2202,3818 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C16C49C9-4843-476F-A284-418FFA1EFBFA}">
-  <dimension ref="A1:V89"/>
+  <dimension ref="A1:O89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="2"/>
-    <col min="4" max="4" width="18" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" style="7"/>
-    <col min="6" max="7" width="11.5546875" style="2"/>
-    <col min="8" max="8" width="17.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.5546875" style="2"/>
-    <col min="13" max="13" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="11.5546875" style="2"/>
+    <col min="1" max="1" width="16.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="11.5546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="O1" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2" s="11">
+        <v>1800000001</v>
+      </c>
+      <c r="D2" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="H2" s="13">
+        <v>1208021050</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K2" s="4">
+        <v>8671</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="16">
+        <v>7.3</v>
+      </c>
+      <c r="N2" s="4">
+        <v>40</v>
+      </c>
+      <c r="O2" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C3" s="11">
+        <v>1800000002</v>
+      </c>
+      <c r="D3" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="H3" s="13">
+        <v>1211034239</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K3" s="4">
+        <v>8481</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="16">
+        <v>11.5</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C4" s="11">
+        <v>1800000003</v>
+      </c>
+      <c r="D4" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="H4" s="13">
+        <v>14511084</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K4" s="4">
+        <v>3960</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="16">
+        <v>190.5</v>
+      </c>
+      <c r="N4" s="4">
+        <v>20</v>
+      </c>
+      <c r="O4" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1800000003</v>
+      </c>
+      <c r="D5" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="H5" s="13">
+        <v>8899078</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K5" s="4">
+        <v>3895</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="16">
+        <v>483.00000000000006</v>
+      </c>
+      <c r="N5" s="4">
+        <v>20</v>
+      </c>
+      <c r="O5" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="D6" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="H6" s="13">
+        <v>130628815</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K6" s="4">
+        <v>2396.54</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="16">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>25</v>
+      </c>
+      <c r="O6" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C7" s="11">
+        <v>1800000005</v>
+      </c>
+      <c r="D7" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="H7" s="13">
+        <v>171430644</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K7" s="4">
+        <v>1208</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="16">
+        <v>20</v>
+      </c>
+      <c r="N7" s="4">
+        <v>25</v>
+      </c>
+      <c r="O7" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C8" s="11">
+        <v>1800000006</v>
+      </c>
+      <c r="D8" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="H8" s="13">
+        <v>8896612</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K8" s="4">
+        <v>4303</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="16">
+        <v>59.4</v>
+      </c>
+      <c r="N8" s="4">
+        <v>5</v>
+      </c>
+      <c r="O8" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="D9" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="H9" s="13">
+        <v>8896617</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K9" s="4">
+        <v>3064</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="16">
+        <v>27.3</v>
+      </c>
+      <c r="N9" s="4">
+        <v>20</v>
+      </c>
+      <c r="O9" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C10" s="11">
+        <v>1800000008</v>
+      </c>
+      <c r="D10" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H10" s="13">
+        <v>12299219</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K10" s="4">
+        <v>3242</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="16">
+        <v>97.200000000000017</v>
+      </c>
+      <c r="N10" s="4">
+        <v>40</v>
+      </c>
+      <c r="O10" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C11" s="11">
+        <v>1800000009</v>
+      </c>
+      <c r="D11" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="P1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="F11" s="4"/>
+      <c r="G11" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H11" s="13">
+        <v>8896620</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K11" s="4">
+        <v>1891</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4">
+        <v>25</v>
+      </c>
+      <c r="O11" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C12" s="11">
+        <v>1800000009</v>
+      </c>
+      <c r="D12" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H12" s="13">
+        <v>1211034231</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K12" s="4">
+        <v>6995</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C13" s="11">
+        <v>1800000010</v>
+      </c>
+      <c r="D13" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H13" s="13">
+        <v>1211033708</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K13" s="4">
+        <v>5588</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="16">
+        <v>14.4</v>
+      </c>
+      <c r="N13" s="4">
+        <v>40</v>
+      </c>
+      <c r="O13" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C14" s="11">
+        <v>1800000011</v>
+      </c>
+      <c r="D14" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H14" s="13">
+        <v>11817151</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K14" s="4">
+        <v>1238</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="16">
+        <v>55</v>
+      </c>
+      <c r="N14" s="4">
+        <v>40</v>
+      </c>
+      <c r="O14" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C15" s="11">
+        <v>1800000012</v>
+      </c>
+      <c r="D15" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K15" s="4">
+        <v>4698</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="16">
+        <v>92.5</v>
+      </c>
+      <c r="N15" s="4">
+        <v>20</v>
+      </c>
+      <c r="O15" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C16" s="11">
+        <v>1800000013</v>
+      </c>
+      <c r="D16" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K16" s="4">
+        <v>3084.94</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="16">
+        <v>26.85</v>
+      </c>
+      <c r="N16" s="4"/>
+      <c r="O16" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C17" s="11">
+        <v>1800000014</v>
+      </c>
+      <c r="D17" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1686.34</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="16">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="N17" s="4">
+        <v>25</v>
+      </c>
+      <c r="O17" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C18" s="11">
+        <v>1800000015</v>
+      </c>
+      <c r="D18" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H18" s="13">
+        <v>1211033520</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K18" s="4">
+        <v>3565</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="16">
+        <v>15.4</v>
+      </c>
+      <c r="N18" s="4">
+        <v>40</v>
+      </c>
+      <c r="O18" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C19" s="11">
+        <v>1800000016</v>
+      </c>
+      <c r="D19" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H19" s="13">
+        <v>1211033704</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1721</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4">
+        <v>25</v>
+      </c>
+      <c r="O19" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C20" s="11">
+        <v>1800000017</v>
+      </c>
+      <c r="D20" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H20" s="13">
+        <v>1211034233</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K20" s="4">
+        <v>4144</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="16">
+        <v>479.03549999999996</v>
+      </c>
+      <c r="N20" s="4">
+        <v>25</v>
+      </c>
+      <c r="O20" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C21" s="11">
+        <v>1800000017</v>
+      </c>
+      <c r="D21" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H21" s="13">
+        <v>21052411</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K21" s="4">
+        <v>7442.1139999999996</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="16">
+        <v>594.66150000000005</v>
+      </c>
+      <c r="N21" s="4"/>
+      <c r="O21" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="11">
+        <v>1800000018</v>
+      </c>
+      <c r="D22" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="16">
+        <v>85</v>
+      </c>
+      <c r="N22" s="4">
+        <v>40</v>
+      </c>
+      <c r="O22" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C23" s="11">
+        <v>1800000019</v>
+      </c>
+      <c r="D23" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H23" s="13">
+        <v>25295328</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K23" s="4">
+        <v>757.51400000000001</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="16">
+        <v>257.51660000000004</v>
+      </c>
+      <c r="N23" s="4">
+        <v>20</v>
+      </c>
+      <c r="O23" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C24" s="11">
+        <v>1800000019</v>
+      </c>
+      <c r="D24" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="16">
+        <v>28</v>
+      </c>
+      <c r="N24" s="4"/>
+      <c r="O24" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" s="11">
+        <v>1800000020</v>
+      </c>
+      <c r="D25" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K25" s="4">
+        <v>1583.86</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" s="16">
+        <v>183.32799999999997</v>
+      </c>
+      <c r="N25" s="4">
+        <v>25</v>
+      </c>
+      <c r="O25" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C26" s="11">
+        <v>1800000021</v>
+      </c>
+      <c r="D26" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H26" s="13">
+        <v>1211033709</v>
+      </c>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K26" s="4">
+        <v>125</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="16">
+        <v>95</v>
+      </c>
+      <c r="N26" s="4">
+        <v>40</v>
+      </c>
+      <c r="O26" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C27" s="11">
+        <v>1800000022</v>
+      </c>
+      <c r="D27" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H27" s="13">
+        <v>1211033707</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K27" s="4">
+        <v>8681</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="16">
+        <v>136.4</v>
+      </c>
+      <c r="N27" s="4">
+        <v>40</v>
+      </c>
+      <c r="O27" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C28" s="11">
+        <v>1800000023</v>
+      </c>
+      <c r="D28" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H28" s="13">
+        <v>1211034240</v>
+      </c>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K28" s="4">
+        <v>3217</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="16">
         <v>16</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="C2" s="9">
-        <v>1800000001</v>
-      </c>
-      <c r="D2" s="10">
-        <v>31048</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8" t="s">
+      <c r="N28" s="4">
+        <v>40</v>
+      </c>
+      <c r="O28" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C29" s="11">
+        <v>1800000024</v>
+      </c>
+      <c r="D29" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H29" s="13">
+        <v>1208020366</v>
+      </c>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="K2" s="8">
-        <v>8671</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="12">
-        <v>7.2999999999999972</v>
-      </c>
-      <c r="N2" s="8">
-        <v>1</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="P2" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="K29" s="4">
+        <v>9794.23</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="16">
+        <v>1543.0840000000001</v>
+      </c>
+      <c r="N29" s="4">
+        <v>20</v>
+      </c>
+      <c r="O29" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C30" s="11">
+        <v>1800000025</v>
+      </c>
+      <c r="D30" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K30" s="4">
+        <v>88.31</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="16">
+        <v>231.9</v>
+      </c>
+      <c r="N30" s="4">
+        <v>40</v>
+      </c>
+      <c r="O30" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C31" s="11">
+        <v>1800000026</v>
+      </c>
+      <c r="D31" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H31" s="13">
+        <v>1211036816</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K31" s="4">
+        <v>3840</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="16">
+        <v>173</v>
+      </c>
+      <c r="N31" s="4">
+        <v>40</v>
+      </c>
+      <c r="O31" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C32" s="11">
+        <v>1800000026</v>
+      </c>
+      <c r="D32" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H32" s="13">
+        <v>1211036811</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K32" s="4">
+        <v>58</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" s="16">
+        <v>8</v>
+      </c>
+      <c r="N32" s="4"/>
+      <c r="O32" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C33" s="11">
+        <v>1800000027</v>
+      </c>
+      <c r="D33" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H33" s="13">
+        <v>1211034334</v>
+      </c>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K33" s="4">
+        <v>1948</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="16">
+        <v>3</v>
+      </c>
+      <c r="N33" s="4">
+        <v>25</v>
+      </c>
+      <c r="O33" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C34" s="11">
+        <v>1800000028</v>
+      </c>
+      <c r="D34" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K34" s="4">
+        <v>0</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" s="16">
+        <v>258</v>
+      </c>
+      <c r="N34" s="4">
+        <v>40</v>
+      </c>
+      <c r="O34" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1800000029</v>
+      </c>
+      <c r="D35" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" s="16">
+        <v>5</v>
+      </c>
+      <c r="N35" s="4">
+        <v>40</v>
+      </c>
+      <c r="O35" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C36" s="11">
+        <v>1800000030</v>
+      </c>
+      <c r="D36" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K36" s="4">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="16">
+        <v>35</v>
+      </c>
+      <c r="N36" s="4">
+        <v>40</v>
+      </c>
+      <c r="O36" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="11">
+        <v>1800000031</v>
+      </c>
+      <c r="D37" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H37" s="13">
+        <v>1211034238</v>
+      </c>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K37" s="4">
+        <v>223</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="16">
+        <v>45</v>
+      </c>
+      <c r="N37" s="4">
+        <v>5</v>
+      </c>
+      <c r="O37" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C38" s="11">
+        <v>1800000032</v>
+      </c>
+      <c r="D38" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H38" s="13">
+        <v>1211034232</v>
+      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K38" s="4">
+        <v>937</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="16">
+        <v>75</v>
+      </c>
+      <c r="N38" s="4"/>
+      <c r="O38" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="D39" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H39" s="13">
+        <v>1208020313</v>
+      </c>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K39" s="4">
+        <v>7236</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M39" s="16">
+        <v>15.6</v>
+      </c>
+      <c r="N39" s="4"/>
+      <c r="O39" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C40" s="11">
+        <v>1800000034</v>
+      </c>
+      <c r="D40" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H40" s="13">
+        <v>1208020318</v>
+      </c>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K40" s="4">
+        <v>4772</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M40" s="16">
+        <v>0</v>
+      </c>
+      <c r="N40" s="4">
+        <v>5</v>
+      </c>
+      <c r="O40" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="C3" s="9">
-        <v>1800000002</v>
-      </c>
-      <c r="D3" s="10">
+      <c r="C41" s="11">
+        <v>1800000035</v>
+      </c>
+      <c r="D41" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H41" s="13">
+        <v>1208020320</v>
+      </c>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K41" s="4">
+        <v>6339</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M41" s="16">
+        <v>0</v>
+      </c>
+      <c r="N41" s="4"/>
+      <c r="O41" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C42" s="11">
+        <v>1800000036</v>
+      </c>
+      <c r="D42" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H42" s="13">
+        <v>1208020314</v>
+      </c>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K42" s="4">
+        <v>3171</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" s="16">
+        <v>0</v>
+      </c>
+      <c r="N42" s="4">
+        <v>20</v>
+      </c>
+      <c r="O42" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C43" s="11">
+        <v>1800000036</v>
+      </c>
+      <c r="D43" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H43" s="13">
+        <v>1208020827</v>
+      </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K43" s="4">
+        <v>600</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="16">
+        <v>10</v>
+      </c>
+      <c r="N43" s="4">
+        <v>20</v>
+      </c>
+      <c r="O43" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C44" s="11">
+        <v>1800000037</v>
+      </c>
+      <c r="D44" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H44" s="13">
+        <v>1208020315</v>
+      </c>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K44" s="4">
+        <v>8583</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" s="16">
+        <v>5</v>
+      </c>
+      <c r="N44" s="4"/>
+      <c r="O44" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C45" s="11">
+        <v>1800000038</v>
+      </c>
+      <c r="D45" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H45" s="13">
+        <v>1208020317</v>
+      </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K45" s="4">
+        <v>7861</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M45" s="16">
+        <v>0</v>
+      </c>
+      <c r="N45" s="4"/>
+      <c r="O45" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C46" s="11">
+        <v>1800000039</v>
+      </c>
+      <c r="D46" s="7">
         <v>20090</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>414</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8" t="s">
+      <c r="E46" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H46" s="13">
+        <v>1208020311</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="J46" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="K3" s="8">
-        <v>8481</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="12">
-        <v>11.5</v>
-      </c>
-      <c r="N3" s="8">
-        <v>1</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="P3" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="K46" s="4">
+        <v>1778</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" s="16">
+        <v>0</v>
+      </c>
+      <c r="N46" s="4"/>
+      <c r="O46" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C47" s="11">
+        <v>1800000039</v>
+      </c>
+      <c r="D47" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H47" s="13">
+        <v>1208020368</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K47" s="4">
+        <v>1671</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="16">
+        <v>0</v>
+      </c>
+      <c r="N47" s="4"/>
+      <c r="O47" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C48" s="11">
+        <v>1800000040</v>
+      </c>
+      <c r="D48" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H48" s="13">
+        <v>1208020826</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K48" s="4">
+        <v>3876</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" s="16">
+        <v>0</v>
+      </c>
+      <c r="N48" s="4"/>
+      <c r="O48" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C49" s="11">
+        <v>1800000041</v>
+      </c>
+      <c r="D49" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H49" s="13">
+        <v>1208020319</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K49" s="4">
+        <v>6538</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M49" s="16">
+        <v>0</v>
+      </c>
+      <c r="N49" s="4"/>
+      <c r="O49" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="D50" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H50" s="13">
+        <v>1208020828</v>
+      </c>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K50" s="4">
+        <v>11190</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="16">
+        <v>0</v>
+      </c>
+      <c r="N50" s="4"/>
+      <c r="O50" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="D51" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H51" s="13">
+        <v>1208020369</v>
+      </c>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K51" s="4">
+        <v>5031</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M51" s="16">
+        <v>92.5</v>
+      </c>
+      <c r="N51" s="4">
+        <v>40</v>
+      </c>
+      <c r="O51" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>505</v>
+      </c>
+      <c r="D52" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K52" s="4">
+        <v>5382</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M52" s="16">
+        <v>0</v>
+      </c>
+      <c r="N52" s="4">
+        <v>5</v>
+      </c>
+      <c r="O52" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C53" s="11">
+        <v>1800000045</v>
+      </c>
+      <c r="D53" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H53" s="13">
+        <v>1603004786</v>
+      </c>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K53" s="4">
+        <v>1551.4680000000001</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="16">
+        <v>8</v>
+      </c>
+      <c r="N53" s="4"/>
+      <c r="O53" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C54" s="11">
+        <v>1800000046</v>
+      </c>
+      <c r="D54" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H54" s="13">
+        <v>1208020824</v>
+      </c>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K54" s="4">
+        <v>5109</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M54" s="16">
+        <v>2</v>
+      </c>
+      <c r="N54" s="4"/>
+      <c r="O54" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C55" s="11">
+        <v>1800000047</v>
+      </c>
+      <c r="D55" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H55" s="13">
+        <v>1208020830</v>
+      </c>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K55" s="4">
+        <v>841</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M55" s="16">
+        <v>4</v>
+      </c>
+      <c r="N55" s="4">
+        <v>40</v>
+      </c>
+      <c r="O55" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C56" s="11">
+        <v>1800000048</v>
+      </c>
+      <c r="D56" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H56" s="13">
+        <v>1211034237</v>
+      </c>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K56" s="4">
+        <v>1446</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="16">
+        <v>4</v>
+      </c>
+      <c r="N56" s="4">
+        <v>5</v>
+      </c>
+      <c r="O56" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C57" s="11">
+        <v>1800000049</v>
+      </c>
+      <c r="D57" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H57" s="13">
+        <v>1208020821</v>
+      </c>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K57" s="4">
+        <v>4277</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M57" s="16">
+        <v>0</v>
+      </c>
+      <c r="N57" s="4">
+        <v>40</v>
+      </c>
+      <c r="O57" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C58" s="11">
+        <v>1800000050</v>
+      </c>
+      <c r="D58" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H58" s="13">
+        <v>1208020822</v>
+      </c>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K58" s="4">
+        <v>2242</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M58" s="16">
+        <v>0</v>
+      </c>
+      <c r="N58" s="4"/>
+      <c r="O58" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="D59" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H59" s="13">
+        <v>1208020823</v>
+      </c>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K59" s="4">
+        <v>767</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M59" s="16">
+        <v>0</v>
+      </c>
+      <c r="N59" s="4">
+        <v>5</v>
+      </c>
+      <c r="O59" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>511</v>
+      </c>
+      <c r="D60" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H60" s="13">
+        <v>1211034236</v>
+      </c>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K60" s="4">
+        <v>2991</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="16">
+        <v>0</v>
+      </c>
+      <c r="N60" s="4"/>
+      <c r="O60" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C4" s="9">
-        <v>1800000003</v>
-      </c>
-      <c r="D4" s="10">
-        <v>31048</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>415</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8" t="s">
+      <c r="B61" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C61" s="11">
+        <v>1800000053</v>
+      </c>
+      <c r="D61" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H61" s="13">
+        <v>1208020312</v>
+      </c>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="K4" s="8">
-        <v>3960</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="12">
-        <v>160</v>
-      </c>
-      <c r="N4" s="8">
-        <v>12</v>
-      </c>
-      <c r="O4" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="P4" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C5" s="9">
-        <v>1800000003</v>
-      </c>
-      <c r="D5" s="10">
-        <v>31048</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>416</v>
-      </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8" t="s">
+      <c r="K61" s="4">
+        <v>4233</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="16">
+        <v>51.8</v>
+      </c>
+      <c r="N61" s="4">
+        <v>20</v>
+      </c>
+      <c r="O61" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C62" s="11">
+        <v>1800000054</v>
+      </c>
+      <c r="D62" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H62" s="13">
+        <v>1203020825</v>
+      </c>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="K5" s="8">
-        <v>3895</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="12">
-        <v>397.91</v>
-      </c>
-      <c r="N5" s="8">
-        <v>12</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="P5" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C6" s="9">
-        <v>1800000004</v>
-      </c>
-      <c r="D6" s="10">
-        <v>31048</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
+      <c r="K62" s="4">
+        <v>6575</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M62" s="16">
+        <v>0</v>
+      </c>
+      <c r="N62" s="4">
+        <v>20</v>
+      </c>
+      <c r="O62" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C63" s="11">
+        <v>1800000055</v>
+      </c>
+      <c r="D63" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H63" s="13">
+        <v>1208021044</v>
+      </c>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="K6" s="8">
-        <v>2396.54</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="12">
-        <v>0</v>
-      </c>
-      <c r="N6" s="8">
-        <v>0</v>
-      </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C7" s="9">
-        <v>1800000005</v>
-      </c>
-      <c r="D7" s="10">
+      <c r="K63" s="4">
+        <v>2384</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M63" s="16">
+        <v>15</v>
+      </c>
+      <c r="N63" s="4">
+        <v>20</v>
+      </c>
+      <c r="O63" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C64" s="11">
+        <v>1800000056</v>
+      </c>
+      <c r="D64" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H64" s="13">
+        <v>1208021048</v>
+      </c>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K64" s="4">
+        <v>4975</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M64" s="16">
+        <v>11.1</v>
+      </c>
+      <c r="N64" s="4"/>
+      <c r="O64" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C65" s="11">
+        <v>1800000057</v>
+      </c>
+      <c r="D65" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H65" s="13">
+        <v>1208021047</v>
+      </c>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K65" s="4">
+        <v>4070</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M65" s="16">
+        <v>51.5</v>
+      </c>
+      <c r="N65" s="4">
+        <v>40</v>
+      </c>
+      <c r="O65" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C66" s="11">
+        <v>1800000058</v>
+      </c>
+      <c r="D66" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H66" s="13">
+        <v>1208020829</v>
+      </c>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K66" s="4">
+        <v>6031</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M66" s="16">
+        <v>0</v>
+      </c>
+      <c r="N66" s="4"/>
+      <c r="O66" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C67" s="11">
+        <v>1800000059</v>
+      </c>
+      <c r="D67" s="7">
         <v>20090</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>418</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="H7" s="8" t="s">
+      <c r="E67" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H67" s="13">
+        <v>1208020362</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K67" s="4">
+        <v>5998</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" s="16">
+        <v>0</v>
+      </c>
+      <c r="N67" s="4"/>
+      <c r="O67" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C68" s="11">
+        <v>1800000059</v>
+      </c>
+      <c r="D68" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K68" s="4">
+        <v>0</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M68" s="16">
+        <v>8</v>
+      </c>
+      <c r="N68" s="4"/>
+      <c r="O68" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C69" s="11">
+        <v>1800000060</v>
+      </c>
+      <c r="D69" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H69" s="13">
+        <v>1208020365</v>
+      </c>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K69" s="4">
+        <v>1080</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M69" s="16">
+        <v>5</v>
+      </c>
+      <c r="N69" s="4">
         <v>40</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8" t="s">
+      <c r="O69" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C70" s="11">
+        <v>1800000061</v>
+      </c>
+      <c r="D70" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H70" s="13">
+        <v>8899276</v>
+      </c>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="K7" s="8">
-        <v>1208</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="12">
-        <v>36</v>
-      </c>
-      <c r="N7" s="8">
-        <v>7</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="P7" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="K70" s="4">
+        <v>376</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" s="16">
+        <v>0</v>
+      </c>
+      <c r="N70" s="4"/>
+      <c r="O70" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C71" s="11">
+        <v>1800000062</v>
+      </c>
+      <c r="D71" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H71" s="13">
+        <v>14511085</v>
+      </c>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K71" s="4">
+        <v>889</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" s="16">
+        <v>8</v>
+      </c>
+      <c r="N71" s="4">
+        <v>5</v>
+      </c>
+      <c r="O71" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C72" s="11">
+        <v>1800000063</v>
+      </c>
+      <c r="D72" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K72" s="4">
+        <v>780.45</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" s="16">
+        <v>0</v>
+      </c>
+      <c r="N72" s="4"/>
+      <c r="O72" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C73" s="11">
+        <v>1800000064</v>
+      </c>
+      <c r="D73" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H73" s="13">
+        <v>1208020367</v>
+      </c>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K73" s="4">
+        <v>4632</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73" s="16">
+        <v>129.80000000000001</v>
+      </c>
+      <c r="N73" s="4">
+        <v>20</v>
+      </c>
+      <c r="O73" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C74" s="11">
+        <v>1800000065</v>
+      </c>
+      <c r="D74" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H74" s="13">
+        <v>1208022066</v>
+      </c>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K74" s="4">
+        <v>7619</v>
+      </c>
+      <c r="L74" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M74" s="16">
+        <v>2.8</v>
+      </c>
+      <c r="N74" s="4">
+        <v>20</v>
+      </c>
+      <c r="O74" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C75" s="11">
+        <v>1800000066</v>
+      </c>
+      <c r="D75" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H75" s="13">
+        <v>1208021049</v>
+      </c>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K75" s="4">
+        <v>2176</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M75" s="16">
+        <v>50.8</v>
+      </c>
+      <c r="N75" s="4"/>
+      <c r="O75" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C76" s="11">
+        <v>1800000067</v>
+      </c>
+      <c r="D76" s="7">
+        <v>20090</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H76" s="13">
+        <v>1208022061</v>
+      </c>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K76" s="4">
+        <v>461</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M76" s="16">
+        <v>0</v>
+      </c>
+      <c r="N76" s="4">
+        <v>20</v>
+      </c>
+      <c r="O76" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C77" s="11">
+        <v>1800000068</v>
+      </c>
+      <c r="D77" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H77" s="13">
+        <v>1208021046</v>
+      </c>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K77" s="4">
+        <v>3046</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M77" s="16">
+        <v>0</v>
+      </c>
+      <c r="N77" s="4"/>
+      <c r="O77" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C78" s="11">
+        <v>1800000069</v>
+      </c>
+      <c r="D78" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H78" s="13">
+        <v>1208020363</v>
+      </c>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K78" s="4">
+        <v>4728</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M78" s="16">
+        <v>0</v>
+      </c>
+      <c r="N78" s="4"/>
+      <c r="O78" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C79" s="11">
+        <v>1800000070</v>
+      </c>
+      <c r="D79" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H79" s="13">
+        <v>1208020364</v>
+      </c>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K79" s="4">
+        <v>2136</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M79" s="16">
+        <v>0</v>
+      </c>
+      <c r="N79" s="4">
+        <v>5</v>
+      </c>
+      <c r="O79" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C80" s="11">
+        <v>1800000071</v>
+      </c>
+      <c r="D80" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H80" s="13">
+        <v>2540886190</v>
+      </c>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K80" s="4">
+        <v>476</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M80" s="16">
+        <v>124.7</v>
+      </c>
+      <c r="N80" s="4">
+        <v>20</v>
+      </c>
+      <c r="O80" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1800000006</v>
-      </c>
-      <c r="D8" s="10">
-        <v>20090</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>419</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
+      <c r="B81" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C81" s="11">
+        <v>1800000072</v>
+      </c>
+      <c r="D81" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H81" s="13">
+        <v>1208021041</v>
+      </c>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="K8" s="8">
-        <v>4303</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="12">
-        <v>47</v>
-      </c>
-      <c r="N8" s="8">
-        <v>8</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="P8" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="K81" s="4">
+        <v>4510</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M81" s="16">
+        <v>5</v>
+      </c>
+      <c r="N81" s="4">
+        <v>20</v>
+      </c>
+      <c r="O81" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C82" s="11">
+        <v>1800000073</v>
+      </c>
+      <c r="D82" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H82" s="13">
+        <v>1208021045</v>
+      </c>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K82" s="4">
+        <v>1375</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M82" s="16">
+        <v>15</v>
+      </c>
+      <c r="N82" s="4"/>
+      <c r="O82" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C83" s="11">
+        <v>1800000074</v>
+      </c>
+      <c r="D83" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H83" s="13">
+        <v>1208021043</v>
+      </c>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K83" s="4">
+        <v>2170</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M83" s="16">
+        <v>182.3</v>
+      </c>
+      <c r="N83" s="4">
+        <v>40</v>
+      </c>
+      <c r="O83" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C84" s="11">
+        <v>1800000075</v>
+      </c>
+      <c r="D84" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H84" s="13">
+        <v>1208022062</v>
+      </c>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K84" s="4">
+        <v>4734</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M84" s="16">
+        <v>0</v>
+      </c>
+      <c r="N84" s="4"/>
+      <c r="O84" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C85" s="11">
+        <v>1800000076</v>
+      </c>
+      <c r="D85" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H85" s="13">
+        <v>1208022063</v>
+      </c>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K85" s="4">
+        <v>2648</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M85" s="16">
+        <v>0</v>
+      </c>
+      <c r="N85" s="4"/>
+      <c r="O85" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B86" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C86" s="11">
+        <v>1800000077</v>
+      </c>
+      <c r="D86" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H86" s="13">
+        <v>1208020844</v>
+      </c>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K86" s="4">
+        <v>2561</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M86" s="16">
+        <v>40</v>
+      </c>
+      <c r="O86" s="10">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C87" s="11">
+        <v>1800000078</v>
+      </c>
+      <c r="D87" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H87" s="13">
+        <v>1208020370</v>
+      </c>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K87" s="4">
+        <v>4407</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M87" s="14">
+        <v>180.39999999999998</v>
+      </c>
+      <c r="N87" s="14">
+        <v>40</v>
+      </c>
+      <c r="O87" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B88" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C9" s="9">
-        <v>1800000007</v>
-      </c>
-      <c r="D9" s="10">
-        <v>31048</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8" t="s">
+      <c r="C88" s="11">
+        <v>1800000079</v>
+      </c>
+      <c r="D88" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H88" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="K9" s="8">
-        <v>3064</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="12">
-        <v>27.3</v>
-      </c>
-      <c r="N9" s="8">
-        <v>5</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="P9" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="C10" s="9">
-        <v>1800000008</v>
-      </c>
-      <c r="D10" s="10">
-        <v>20090</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8" t="s">
+      <c r="K88" s="4">
+        <v>0</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M88" s="14">
+        <v>0</v>
+      </c>
+      <c r="N88" s="14">
+        <v>40</v>
+      </c>
+      <c r="O88" s="9">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C89" s="11">
+        <v>1800000080</v>
+      </c>
+      <c r="D89" s="7">
+        <v>31048</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H89" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="K10" s="8">
-        <v>3242</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="12">
-        <v>70.2</v>
-      </c>
-      <c r="N10" s="8">
-        <v>10</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="P10" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="C11" s="9">
-        <v>1800000009</v>
-      </c>
-      <c r="D11" s="10">
-        <v>20090</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>422</v>
-      </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="K11" s="8">
-        <v>1891</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="12">
-        <v>0</v>
-      </c>
-      <c r="N11" s="8">
-        <v>0</v>
-      </c>
-      <c r="O11" s="8"/>
-      <c r="P11" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="C12" s="9">
-        <v>1800000009</v>
-      </c>
-      <c r="D12" s="10">
-        <v>20090</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>423</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="K12" s="8">
-        <v>6995</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="8">
-        <v>0</v>
-      </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="C13" s="9">
-        <v>1800000010</v>
-      </c>
-      <c r="D13" s="10">
-        <v>31048</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>427</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="K13" s="8">
-        <v>5588</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" s="12">
-        <v>10</v>
-      </c>
-      <c r="N13" s="8">
-        <v>1</v>
-      </c>
-      <c r="O13" s="8"/>
-      <c r="P13" s="13">
-        <v>44562</v>
-      </c>
-      <c r="S13" s="9">
-        <v>12</v>
-      </c>
-      <c r="T13" s="9">
-        <v>5</v>
-      </c>
-      <c r="U13" s="9">
-        <v>5588</v>
-      </c>
-      <c r="V13" s="9">
-        <v>5561</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="C14" s="9">
-        <v>1800000011</v>
-      </c>
-      <c r="D14" s="10">
-        <v>31048</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>425</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="K14" s="8">
-        <v>1238</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="12">
-        <v>60</v>
-      </c>
-      <c r="N14" s="8">
-        <v>5</v>
-      </c>
-      <c r="O14" s="8"/>
-      <c r="P14" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C15" s="9">
-        <v>1800000012</v>
-      </c>
-      <c r="D15" s="10">
-        <v>31048</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>428</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="K15" s="8">
-        <v>4698</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="12">
-        <v>87.200000000000017</v>
-      </c>
-      <c r="N15" s="8">
-        <v>7</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="P15" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="C16" s="9">
-        <v>1800000013</v>
-      </c>
-      <c r="D16" s="10">
-        <v>31048</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>424</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="K16" s="8">
-        <v>3084.94</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="12">
-        <v>26.85</v>
-      </c>
-      <c r="N16" s="8">
-        <v>1</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="P16" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C17" s="9">
-        <v>1800000014</v>
-      </c>
-      <c r="D17" s="10">
-        <v>31048</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>429</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="K17" s="8">
-        <v>1686.34</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" s="12">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="N17" s="8">
-        <v>2</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="P17" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C18" s="9">
-        <v>1800000015</v>
-      </c>
-      <c r="D18" s="10">
-        <v>31048</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>426</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="K18" s="8">
-        <v>3565</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="12">
-        <v>15.4</v>
-      </c>
-      <c r="N18" s="8">
-        <v>2</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="P18" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="C19" s="9">
-        <v>1800000016</v>
-      </c>
-      <c r="D19" s="10">
-        <v>20090</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>430</v>
-      </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="K19" s="8">
-        <v>1721</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" s="12">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8">
-        <v>0</v>
-      </c>
-      <c r="O19" s="8"/>
-      <c r="P19" s="13">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="C20" s="16">
-        <v>1800000017</v>
-      </c>
-      <c r="D20" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>431</v>
-      </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K20" s="15">
-        <v>4144</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="19">
-        <v>335.28</v>
-      </c>
-      <c r="N20" s="15">
-        <v>7</v>
-      </c>
-      <c r="O20" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="P20" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="C21" s="16">
-        <v>1800000017</v>
-      </c>
-      <c r="D21" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K21" s="15">
-        <v>7442.1139999999996</v>
-      </c>
-      <c r="L21" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="19">
-        <v>715.33159999999998</v>
-      </c>
-      <c r="N21" s="15">
-        <v>7</v>
-      </c>
-      <c r="O21" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="P21" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
-        <v>504</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="16">
-        <v>1800000018</v>
-      </c>
-      <c r="D22" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>433</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K22" s="15">
-        <v>0</v>
-      </c>
-      <c r="L22" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" s="19">
-        <v>145</v>
-      </c>
-      <c r="N22" s="15">
-        <v>7</v>
-      </c>
-      <c r="O22" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="P22" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="C23" s="16">
-        <v>1800000019</v>
-      </c>
-      <c r="D23" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>434</v>
-      </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K23" s="15">
-        <v>757.51400000000001</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" s="19">
-        <v>119.34270000000001</v>
-      </c>
-      <c r="N23" s="15">
-        <v>7</v>
-      </c>
-      <c r="O23" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="P23" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="C24" s="16">
-        <v>1800000019</v>
-      </c>
-      <c r="D24" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K24" s="15">
-        <v>0</v>
-      </c>
-      <c r="L24" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" s="19">
-        <v>76</v>
-      </c>
-      <c r="N24" s="15">
-        <v>7</v>
-      </c>
-      <c r="O24" s="15" t="s">
-        <v>505</v>
-      </c>
-      <c r="P24" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="C25" s="16">
-        <v>1800000020</v>
-      </c>
-      <c r="D25" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>436</v>
-      </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K25" s="15">
-        <v>1583.86</v>
-      </c>
-      <c r="L25" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" s="19">
-        <v>184.994</v>
-      </c>
-      <c r="N25" s="15">
-        <v>7</v>
-      </c>
-      <c r="O25" s="15" t="s">
-        <v>507</v>
-      </c>
-      <c r="P25" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>338</v>
-      </c>
-      <c r="C26" s="16">
-        <v>1800000021</v>
-      </c>
-      <c r="D26" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K26" s="15">
-        <v>125</v>
-      </c>
-      <c r="L26" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" s="19">
-        <v>95</v>
-      </c>
-      <c r="N26" s="15">
-        <v>7</v>
-      </c>
-      <c r="O26" s="15" t="s">
-        <v>508</v>
-      </c>
-      <c r="P26" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="C27" s="16">
-        <v>1800000022</v>
-      </c>
-      <c r="D27" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>438</v>
-      </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H27" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K27" s="15">
-        <v>8681</v>
-      </c>
-      <c r="L27" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" s="19">
-        <v>123.5</v>
-      </c>
-      <c r="N27" s="15">
-        <v>7</v>
-      </c>
-      <c r="O27" s="15" t="s">
-        <v>507</v>
-      </c>
-      <c r="P27" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>339</v>
-      </c>
-      <c r="C28" s="16">
-        <v>1800000023</v>
-      </c>
-      <c r="D28" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>439</v>
-      </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K28" s="15">
-        <v>3217</v>
-      </c>
-      <c r="L28" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" s="19">
-        <v>16</v>
-      </c>
-      <c r="N28" s="15">
-        <v>4</v>
-      </c>
-      <c r="O28" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="P28" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>340</v>
-      </c>
-      <c r="C29" s="16">
-        <v>1800000024</v>
-      </c>
-      <c r="D29" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>440</v>
-      </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K29" s="15">
-        <v>9794.23</v>
-      </c>
-      <c r="L29" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="19">
-        <v>0</v>
-      </c>
-      <c r="N29" s="15">
-        <v>0</v>
-      </c>
-      <c r="O29" s="15"/>
-      <c r="P29" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="C30" s="16">
-        <v>1800000025</v>
-      </c>
-      <c r="D30" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>441</v>
-      </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K30" s="15">
-        <v>88.31</v>
-      </c>
-      <c r="L30" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="19">
-        <v>85</v>
-      </c>
-      <c r="N30" s="15">
-        <v>7</v>
-      </c>
-      <c r="O30" s="15" t="s">
-        <v>509</v>
-      </c>
-      <c r="P30" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>340</v>
-      </c>
-      <c r="C31" s="16">
-        <v>1800000026</v>
-      </c>
-      <c r="D31" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>442</v>
-      </c>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H31" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K31" s="15">
-        <v>3840</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" s="19">
-        <v>76</v>
-      </c>
-      <c r="N31" s="15">
-        <v>7</v>
-      </c>
-      <c r="O31" s="15" t="s">
-        <v>505</v>
-      </c>
-      <c r="P31" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>340</v>
-      </c>
-      <c r="C32" s="16">
-        <v>1800000026</v>
-      </c>
-      <c r="D32" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>443</v>
-      </c>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K32" s="15">
-        <v>58</v>
-      </c>
-      <c r="L32" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" s="19">
-        <v>8</v>
-      </c>
-      <c r="N32" s="15">
-        <v>2</v>
-      </c>
-      <c r="O32" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="P32" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="C33" s="16">
-        <v>1800000027</v>
-      </c>
-      <c r="D33" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>444</v>
-      </c>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K33" s="15">
-        <v>1948</v>
-      </c>
-      <c r="L33" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" s="19">
-        <v>3</v>
-      </c>
-      <c r="N33" s="15">
-        <v>1</v>
-      </c>
-      <c r="O33" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="P33" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="C34" s="16">
-        <v>1800000028</v>
-      </c>
-      <c r="D34" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>445</v>
-      </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K34" s="15">
-        <v>0</v>
-      </c>
-      <c r="L34" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" s="19">
-        <v>330</v>
-      </c>
-      <c r="N34" s="15">
-        <v>17</v>
-      </c>
-      <c r="O34" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="P34" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="C35" s="16">
-        <v>1800000029</v>
-      </c>
-      <c r="D35" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>446</v>
-      </c>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H35" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K35" s="15">
-        <v>0</v>
-      </c>
-      <c r="L35" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M35" s="19">
-        <v>5</v>
-      </c>
-      <c r="N35" s="15">
-        <v>1</v>
-      </c>
-      <c r="O35" s="15" t="s">
-        <v>511</v>
-      </c>
-      <c r="P35" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="C36" s="16">
-        <v>1800000030</v>
-      </c>
-      <c r="D36" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>447</v>
-      </c>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K36" s="15">
-        <v>0</v>
-      </c>
-      <c r="L36" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" s="19">
-        <v>70</v>
-      </c>
-      <c r="N36" s="15">
-        <v>7</v>
-      </c>
-      <c r="O36" s="15" t="s">
-        <v>512</v>
-      </c>
-      <c r="P36" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="16">
-        <v>1800000031</v>
-      </c>
-      <c r="D37" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>448</v>
-      </c>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K37" s="15">
-        <v>223</v>
-      </c>
-      <c r="L37" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" s="19">
-        <v>45</v>
-      </c>
-      <c r="N37" s="15">
-        <v>7</v>
-      </c>
-      <c r="O37" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="P37" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="C38" s="16">
-        <v>1800000032</v>
-      </c>
-      <c r="D38" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>449</v>
-      </c>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K38" s="15">
-        <v>937</v>
-      </c>
-      <c r="L38" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" s="19">
-        <v>70</v>
-      </c>
-      <c r="N38" s="15">
-        <v>7</v>
-      </c>
-      <c r="O38" s="15" t="s">
-        <v>509</v>
-      </c>
-      <c r="P38" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="C39" s="16">
-        <v>1800000033</v>
-      </c>
-      <c r="D39" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K39" s="15">
-        <v>7236</v>
-      </c>
-      <c r="L39" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M39" s="19">
-        <v>15.6</v>
-      </c>
-      <c r="N39" s="15">
-        <v>0</v>
-      </c>
-      <c r="O39" s="15" t="s">
-        <v>514</v>
-      </c>
-      <c r="P39" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="C40" s="16">
-        <v>1800000034</v>
-      </c>
-      <c r="D40" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>451</v>
-      </c>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K40" s="15">
-        <v>4772</v>
-      </c>
-      <c r="L40" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M40" s="19">
-        <v>0</v>
-      </c>
-      <c r="N40" s="15">
-        <v>0</v>
-      </c>
-      <c r="O40" s="15"/>
-      <c r="P40" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="C41" s="16">
-        <v>1800000035</v>
-      </c>
-      <c r="D41" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>452</v>
-      </c>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H41" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K41" s="15">
-        <v>6339</v>
-      </c>
-      <c r="L41" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M41" s="19">
-        <v>6.6</v>
-      </c>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="C42" s="16">
-        <v>1800000036</v>
-      </c>
-      <c r="D42" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>453</v>
-      </c>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H42" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K42" s="15">
-        <v>3171</v>
-      </c>
-      <c r="L42" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M42" s="19">
-        <v>0</v>
-      </c>
-      <c r="N42" s="15">
-        <v>0</v>
-      </c>
-      <c r="O42" s="15"/>
-      <c r="P42" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="C43" s="16">
-        <v>1800000036</v>
-      </c>
-      <c r="D43" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K43" s="15">
-        <v>600</v>
-      </c>
-      <c r="L43" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" s="19">
-        <v>10</v>
-      </c>
-      <c r="N43" s="15">
-        <v>2</v>
-      </c>
-      <c r="O43" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="P43" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="C44" s="22">
-        <v>1800000037</v>
-      </c>
-      <c r="D44" s="23">
-        <v>31048</v>
-      </c>
-      <c r="E44" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="H44" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="I44" s="21"/>
-      <c r="J44" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="K44" s="21">
-        <v>8583</v>
-      </c>
-      <c r="L44" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M44" s="25">
-        <v>5</v>
-      </c>
-      <c r="N44" s="21"/>
-      <c r="O44" s="21"/>
-      <c r="P44" s="26">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C45" s="16">
-        <v>1800000038</v>
-      </c>
-      <c r="D45" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>456</v>
-      </c>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H45" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K45" s="15">
-        <v>7861</v>
-      </c>
-      <c r="L45" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M45" s="19">
-        <v>0</v>
-      </c>
-      <c r="N45" s="15"/>
-      <c r="O45" s="15"/>
-      <c r="P45" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="C46" s="16">
-        <v>1800000039</v>
-      </c>
-      <c r="D46" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>457</v>
-      </c>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H46" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K46" s="15">
-        <v>1778</v>
-      </c>
-      <c r="L46" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M46" s="19">
-        <v>0</v>
-      </c>
-      <c r="N46" s="15"/>
-      <c r="O46" s="15"/>
-      <c r="P46" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="C47" s="16">
-        <v>1800000039</v>
-      </c>
-      <c r="D47" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>458</v>
-      </c>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H47" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K47" s="15">
-        <v>1671</v>
-      </c>
-      <c r="L47" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M47" s="19">
-        <v>0</v>
-      </c>
-      <c r="N47" s="15"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C48" s="16">
-        <v>1800000040</v>
-      </c>
-      <c r="D48" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>459</v>
-      </c>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H48" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K48" s="15">
-        <v>3876</v>
-      </c>
-      <c r="L48" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M48" s="19">
-        <v>0</v>
-      </c>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15"/>
-      <c r="P48" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="C49" s="16">
-        <v>1800000041</v>
-      </c>
-      <c r="D49" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>460</v>
-      </c>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H49" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K49" s="15">
-        <v>6538</v>
-      </c>
-      <c r="L49" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M49" s="19">
-        <v>0</v>
-      </c>
-      <c r="N49" s="15"/>
-      <c r="O49" s="15"/>
-      <c r="P49" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="C50" s="22">
-        <v>1800000042</v>
-      </c>
-      <c r="D50" s="23">
-        <v>20090</v>
-      </c>
-      <c r="E50" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="H50" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="K50" s="21">
-        <v>11190</v>
-      </c>
-      <c r="L50" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" s="25">
-        <v>0</v>
-      </c>
-      <c r="N50" s="21"/>
-      <c r="O50" s="21"/>
-      <c r="P50" s="26">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>346</v>
-      </c>
-      <c r="C51" s="16">
-        <v>1800000043</v>
-      </c>
-      <c r="D51" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H51" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K51" s="15">
-        <v>5031</v>
-      </c>
-      <c r="L51" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M51" s="19">
-        <v>81</v>
-      </c>
-      <c r="N51" s="15">
-        <v>8</v>
-      </c>
-      <c r="O51" s="15" t="s">
-        <v>516</v>
-      </c>
-      <c r="P51" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="C52" s="16">
-        <v>1800000044</v>
-      </c>
-      <c r="D52" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>463</v>
-      </c>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H52" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K52" s="15">
-        <v>5382</v>
-      </c>
-      <c r="L52" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M52" s="19">
-        <v>0</v>
-      </c>
-      <c r="N52" s="15"/>
-      <c r="O52" s="15"/>
-      <c r="P52" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="C53" s="16">
-        <v>1800000045</v>
-      </c>
-      <c r="D53" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>464</v>
-      </c>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H53" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K53" s="15">
-        <v>1551.4680000000001</v>
-      </c>
-      <c r="L53" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M53" s="19">
-        <v>8</v>
-      </c>
-      <c r="N53" s="15">
-        <v>2</v>
-      </c>
-      <c r="O53" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="P53" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="C54" s="16">
-        <v>1800000046</v>
-      </c>
-      <c r="D54" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H54" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K54" s="15">
-        <v>5109</v>
-      </c>
-      <c r="L54" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M54" s="19">
-        <v>3.9999999999999929</v>
-      </c>
-      <c r="N54" s="15">
-        <v>1</v>
-      </c>
-      <c r="O54" s="15" t="s">
-        <v>517</v>
-      </c>
-      <c r="P54" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C55" s="16">
-        <v>1800000047</v>
-      </c>
-      <c r="D55" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>466</v>
-      </c>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H55" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="I55" s="15"/>
-      <c r="J55" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K55" s="15">
-        <v>841</v>
-      </c>
-      <c r="L55" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M55" s="19">
-        <v>4</v>
-      </c>
-      <c r="N55" s="15">
-        <v>1</v>
-      </c>
-      <c r="O55" s="15" t="s">
-        <v>517</v>
-      </c>
-      <c r="P55" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="C56" s="16">
-        <v>1800000048</v>
-      </c>
-      <c r="D56" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>467</v>
-      </c>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H56" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K56" s="15">
-        <v>1446</v>
-      </c>
-      <c r="L56" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M56" s="19">
-        <v>4</v>
-      </c>
-      <c r="N56" s="15">
-        <v>1</v>
-      </c>
-      <c r="O56" s="15" t="s">
-        <v>517</v>
-      </c>
-      <c r="P56" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="C57" s="16">
-        <v>1800000049</v>
-      </c>
-      <c r="D57" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>468</v>
-      </c>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H57" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K57" s="15">
-        <v>4277</v>
-      </c>
-      <c r="L57" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M57" s="19">
-        <v>0</v>
-      </c>
-      <c r="N57" s="15">
-        <v>0</v>
-      </c>
-      <c r="O57" s="15"/>
-      <c r="P57" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="C58" s="16">
-        <v>1800000050</v>
-      </c>
-      <c r="D58" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>469</v>
-      </c>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H58" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K58" s="15">
-        <v>2242</v>
-      </c>
-      <c r="L58" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M58" s="19">
-        <v>5</v>
-      </c>
-      <c r="N58" s="15">
-        <v>1</v>
-      </c>
-      <c r="O58" s="15" t="s">
-        <v>517</v>
-      </c>
-      <c r="P58" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="C59" s="16">
-        <v>1800000051</v>
-      </c>
-      <c r="D59" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>470</v>
-      </c>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H59" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="I59" s="15"/>
-      <c r="J59" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K59" s="15">
-        <v>767</v>
-      </c>
-      <c r="L59" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M59" s="19">
-        <v>0</v>
-      </c>
-      <c r="N59" s="15">
-        <v>0</v>
-      </c>
-      <c r="O59" s="15"/>
-      <c r="P59" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="B60" s="15" t="s">
-        <v>349</v>
-      </c>
-      <c r="C60" s="16">
-        <v>1800000052</v>
-      </c>
-      <c r="D60" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H60" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="I60" s="15"/>
-      <c r="J60" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K60" s="15">
-        <v>2991</v>
-      </c>
-      <c r="L60" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M60" s="19">
-        <v>0</v>
-      </c>
-      <c r="N60" s="15">
-        <v>0</v>
-      </c>
-      <c r="O60" s="15"/>
-      <c r="P60" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B61" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C61" s="16">
-        <v>1800000053</v>
-      </c>
-      <c r="D61" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H61" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K61" s="15">
-        <v>4233</v>
-      </c>
-      <c r="L61" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" s="19">
-        <v>50</v>
-      </c>
-      <c r="N61" s="15">
-        <v>0</v>
-      </c>
-      <c r="O61" s="15" t="s">
-        <v>518</v>
-      </c>
-      <c r="P61" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B62" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C62" s="16">
-        <v>1800000054</v>
-      </c>
-      <c r="D62" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>473</v>
-      </c>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H62" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K62" s="15">
-        <v>6575</v>
-      </c>
-      <c r="L62" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M62" s="19">
-        <v>0</v>
-      </c>
-      <c r="N62" s="15">
-        <v>0</v>
-      </c>
-      <c r="O62" s="15"/>
-      <c r="P62" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="B63" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="C63" s="22">
-        <v>1800000055</v>
-      </c>
-      <c r="D63" s="23">
-        <v>31048</v>
-      </c>
-      <c r="E63" s="24" t="s">
-        <v>474</v>
-      </c>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="H63" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="K63" s="21">
-        <v>2384</v>
-      </c>
-      <c r="L63" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M63" s="25">
-        <v>45</v>
-      </c>
-      <c r="N63" s="21">
-        <v>2</v>
-      </c>
-      <c r="O63" s="21"/>
-      <c r="P63" s="26">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="15" t="s">
+      <c r="K89" s="4">
+        <v>0</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M89" s="14">
         <v>240</v>
       </c>
-      <c r="B64" s="15" t="s">
-        <v>350</v>
-      </c>
-      <c r="C64" s="16">
-        <v>1800000056</v>
-      </c>
-      <c r="D64" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E64" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H64" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="I64" s="15"/>
-      <c r="J64" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K64" s="15">
-        <v>4975</v>
-      </c>
-      <c r="L64" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M64" s="19">
-        <v>11.1</v>
-      </c>
-      <c r="N64" s="15">
-        <v>2</v>
-      </c>
-      <c r="O64" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="P64" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="B65" s="15" t="s">
-        <v>350</v>
-      </c>
-      <c r="C65" s="16">
-        <v>1800000057</v>
-      </c>
-      <c r="D65" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>476</v>
-      </c>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H65" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K65" s="15">
-        <v>4070</v>
-      </c>
-      <c r="L65" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M65" s="19">
-        <v>50.699999999999996</v>
-      </c>
-      <c r="N65" s="15">
-        <v>3</v>
-      </c>
-      <c r="O65" s="15" t="s">
-        <v>519</v>
-      </c>
-      <c r="P65" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="C66" s="16">
-        <v>1800000058</v>
-      </c>
-      <c r="D66" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H66" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="I66" s="15"/>
-      <c r="J66" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K66" s="15">
-        <v>6031</v>
-      </c>
-      <c r="L66" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M66" s="19">
-        <v>0</v>
-      </c>
-      <c r="N66" s="15">
-        <v>0</v>
-      </c>
-      <c r="O66" s="15"/>
-      <c r="P66" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="B67" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="C67" s="16">
-        <v>1800000059</v>
-      </c>
-      <c r="D67" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>478</v>
-      </c>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H67" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K67" s="15">
-        <v>5998</v>
-      </c>
-      <c r="L67" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M67" s="19">
-        <v>0</v>
-      </c>
-      <c r="N67" s="15">
-        <v>0</v>
-      </c>
-      <c r="O67" s="15"/>
-      <c r="P67" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="B68" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="C68" s="22">
-        <v>1800000059</v>
-      </c>
-      <c r="D68" s="23">
-        <v>20090</v>
-      </c>
-      <c r="E68" s="24" t="s">
-        <v>479</v>
-      </c>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="H68" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="K68" s="21">
-        <v>0</v>
-      </c>
-      <c r="L68" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M68" s="25">
-        <v>16</v>
-      </c>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
-      <c r="P68" s="26">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="B69" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="C69" s="16">
-        <v>1800000060</v>
-      </c>
-      <c r="D69" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>480</v>
-      </c>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H69" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K69" s="15">
-        <v>1080</v>
-      </c>
-      <c r="L69" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M69" s="19">
-        <v>5</v>
-      </c>
-      <c r="N69" s="15">
-        <v>1</v>
-      </c>
-      <c r="O69" s="15" t="s">
-        <v>517</v>
-      </c>
-      <c r="P69" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="C70" s="16">
-        <v>1800000061</v>
-      </c>
-      <c r="D70" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E70" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H70" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K70" s="15">
-        <v>376</v>
-      </c>
-      <c r="L70" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" s="19">
-        <v>0</v>
-      </c>
-      <c r="N70" s="15">
-        <v>0</v>
-      </c>
-      <c r="O70" s="15"/>
-      <c r="P70" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="C71" s="16">
-        <v>1800000062</v>
-      </c>
-      <c r="D71" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E71" s="18" t="s">
-        <v>482</v>
-      </c>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H71" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K71" s="15">
-        <v>889</v>
-      </c>
-      <c r="L71" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M71" s="19">
-        <v>8</v>
-      </c>
-      <c r="N71" s="15">
-        <v>2</v>
-      </c>
-      <c r="O71" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="P71" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="B72" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C72" s="16">
-        <v>1800000063</v>
-      </c>
-      <c r="D72" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E72" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="F72" s="15"/>
-      <c r="G72" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H72" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I72" s="15"/>
-      <c r="J72" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K72" s="15">
-        <v>780.45</v>
-      </c>
-      <c r="L72" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M72" s="19">
-        <v>0</v>
-      </c>
-      <c r="N72" s="15">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15"/>
-      <c r="P72" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="B73" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="C73" s="16">
-        <v>1800000064</v>
-      </c>
-      <c r="D73" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E73" s="18" t="s">
-        <v>484</v>
-      </c>
-      <c r="F73" s="15"/>
-      <c r="G73" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H73" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="I73" s="15"/>
-      <c r="J73" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K73" s="15">
-        <v>4632</v>
-      </c>
-      <c r="L73" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M73" s="19">
-        <v>127</v>
-      </c>
-      <c r="N73" s="15">
-        <v>7</v>
-      </c>
-      <c r="O73" s="15" t="s">
-        <v>521</v>
-      </c>
-      <c r="P73" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B74" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="C74" s="16">
-        <v>1800000065</v>
-      </c>
-      <c r="D74" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E74" s="18" t="s">
-        <v>485</v>
-      </c>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H74" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="I74" s="15"/>
-      <c r="J74" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K74" s="15">
-        <v>7619</v>
-      </c>
-      <c r="L74" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M74" s="19">
-        <v>0</v>
-      </c>
-      <c r="N74" s="15">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15"/>
-      <c r="P74" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="B75" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="C75" s="16">
-        <v>1800000066</v>
-      </c>
-      <c r="D75" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E75" s="18" t="s">
-        <v>486</v>
-      </c>
-      <c r="F75" s="15"/>
-      <c r="G75" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H75" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="I75" s="15"/>
-      <c r="J75" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K75" s="15">
-        <v>2176</v>
-      </c>
-      <c r="L75" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M75" s="19">
-        <v>50.8</v>
-      </c>
-      <c r="N75" s="15">
-        <v>3</v>
-      </c>
-      <c r="O75" s="15"/>
-      <c r="P75" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="B76" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="C76" s="16">
-        <v>1800000067</v>
-      </c>
-      <c r="D76" s="17">
-        <v>20090</v>
-      </c>
-      <c r="E76" s="18" t="s">
-        <v>487</v>
-      </c>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H76" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="I76" s="15"/>
-      <c r="J76" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K76" s="15">
-        <v>461</v>
-      </c>
-      <c r="L76" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M76" s="19">
-        <v>0</v>
-      </c>
-      <c r="N76" s="15">
-        <v>0</v>
-      </c>
-      <c r="O76" s="15"/>
-      <c r="P76" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="B77" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="C77" s="16">
-        <v>1800000068</v>
-      </c>
-      <c r="D77" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E77" s="18" t="s">
-        <v>488</v>
-      </c>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H77" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K77" s="15">
-        <v>3046</v>
-      </c>
-      <c r="L77" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M77" s="19">
-        <v>0</v>
-      </c>
-      <c r="N77" s="15"/>
-      <c r="O77" s="15"/>
-      <c r="P77" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B78" s="15" t="s">
-        <v>289</v>
-      </c>
-      <c r="C78" s="16">
-        <v>1800000069</v>
-      </c>
-      <c r="D78" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E78" s="18" t="s">
-        <v>489</v>
-      </c>
-      <c r="F78" s="15"/>
-      <c r="G78" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H78" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="I78" s="15"/>
-      <c r="J78" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K78" s="15">
-        <v>4728</v>
-      </c>
-      <c r="L78" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" s="19">
-        <v>0</v>
-      </c>
-      <c r="N78" s="15"/>
-      <c r="O78" s="15"/>
-      <c r="P78" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="15" t="s">
-        <v>293</v>
-      </c>
-      <c r="B79" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="C79" s="16">
-        <v>1800000070</v>
-      </c>
-      <c r="D79" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E79" s="18" t="s">
-        <v>490</v>
-      </c>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H79" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="I79" s="15"/>
-      <c r="J79" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K79" s="15">
-        <v>2136</v>
-      </c>
-      <c r="L79" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M79" s="19">
-        <v>0</v>
-      </c>
-      <c r="N79" s="15"/>
-      <c r="O79" s="15"/>
-      <c r="P79" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="B80" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="C80" s="16">
-        <v>1800000071</v>
-      </c>
-      <c r="D80" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E80" s="18" t="s">
-        <v>491</v>
-      </c>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H80" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="I80" s="15"/>
-      <c r="J80" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K80" s="15">
-        <v>476</v>
-      </c>
-      <c r="L80" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M80" s="19">
-        <v>123</v>
-      </c>
-      <c r="N80" s="15">
-        <v>7</v>
-      </c>
-      <c r="O80" s="15" t="s">
-        <v>521</v>
-      </c>
-      <c r="P80" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B81" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="C81" s="16">
-        <v>1800000072</v>
-      </c>
-      <c r="D81" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E81" s="18" t="s">
-        <v>492</v>
-      </c>
-      <c r="F81" s="15"/>
-      <c r="G81" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H81" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="I81" s="15"/>
-      <c r="J81" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K81" s="15">
-        <v>4510</v>
-      </c>
-      <c r="L81" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M81" s="19">
-        <v>5</v>
-      </c>
-      <c r="N81" s="15">
-        <v>1</v>
-      </c>
-      <c r="O81" s="15" t="s">
-        <v>522</v>
-      </c>
-      <c r="P81" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B82" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C82" s="16">
-        <v>1800000073</v>
-      </c>
-      <c r="D82" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E82" s="18" t="s">
-        <v>493</v>
-      </c>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H82" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="I82" s="15"/>
-      <c r="J82" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K82" s="15">
-        <v>1375</v>
-      </c>
-      <c r="L82" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M82" s="19">
-        <v>35</v>
-      </c>
-      <c r="N82" s="15">
-        <v>7</v>
-      </c>
-      <c r="O82" s="15" t="s">
-        <v>523</v>
-      </c>
-      <c r="P82" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="B83" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="C83" s="16">
-        <v>1800000074</v>
-      </c>
-      <c r="D83" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E83" s="18" t="s">
-        <v>494</v>
-      </c>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H83" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="I83" s="15"/>
-      <c r="J83" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K83" s="15">
-        <v>2170</v>
-      </c>
-      <c r="L83" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M83" s="19">
-        <v>175.9</v>
-      </c>
-      <c r="N83" s="15">
-        <v>12</v>
-      </c>
-      <c r="O83" s="15" t="s">
-        <v>521</v>
-      </c>
-      <c r="P83" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="B84" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="C84" s="16">
-        <v>1800000075</v>
-      </c>
-      <c r="D84" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E84" s="18" t="s">
-        <v>495</v>
-      </c>
-      <c r="F84" s="15"/>
-      <c r="G84" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H84" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="I84" s="15"/>
-      <c r="J84" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K84" s="15">
-        <v>4734</v>
-      </c>
-      <c r="L84" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M84" s="19">
-        <v>0</v>
-      </c>
-      <c r="N84" s="15">
-        <v>0</v>
-      </c>
-      <c r="O84" s="15"/>
-      <c r="P84" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="B85" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="C85" s="16">
-        <v>1800000076</v>
-      </c>
-      <c r="D85" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E85" s="18" t="s">
-        <v>496</v>
-      </c>
-      <c r="F85" s="15"/>
-      <c r="G85" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H85" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="I85" s="15"/>
-      <c r="J85" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K85" s="15">
-        <v>2648</v>
-      </c>
-      <c r="L85" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M85" s="19">
-        <v>0</v>
-      </c>
-      <c r="N85" s="15">
-        <v>0</v>
-      </c>
-      <c r="O85" s="15"/>
-      <c r="P85" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B86" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="C86" s="22">
-        <v>1800000077</v>
-      </c>
-      <c r="D86" s="23">
-        <v>31048</v>
-      </c>
-      <c r="E86" s="24" t="s">
-        <v>497</v>
-      </c>
-      <c r="F86" s="21"/>
-      <c r="G86" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="H86" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="I86" s="21"/>
-      <c r="J86" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="K86" s="21">
-        <v>2561</v>
-      </c>
-      <c r="L86" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M86" s="25">
-        <v>65</v>
-      </c>
-      <c r="N86" s="21">
-        <v>1</v>
-      </c>
-      <c r="O86" s="21" t="s">
-        <v>524</v>
-      </c>
-      <c r="P86" s="27">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="15" t="s">
-        <v>359</v>
-      </c>
-      <c r="B87" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="C87" s="16">
-        <v>1800000078</v>
-      </c>
-      <c r="D87" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E87" s="18" t="s">
-        <v>498</v>
-      </c>
-      <c r="F87" s="15"/>
-      <c r="G87" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H87" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="I87" s="15"/>
-      <c r="J87" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K87" s="15">
-        <v>4407</v>
-      </c>
-      <c r="L87" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M87" s="19">
-        <v>152.79999999999998</v>
-      </c>
-      <c r="N87" s="15">
-        <v>12</v>
-      </c>
-      <c r="O87" s="15" t="s">
-        <v>521</v>
-      </c>
-      <c r="P87" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="B88" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="C88" s="16">
-        <v>1800000079</v>
-      </c>
-      <c r="D88" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E88" s="18" t="s">
-        <v>499</v>
-      </c>
-      <c r="F88" s="15"/>
-      <c r="G88" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H88" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="I88" s="15"/>
-      <c r="J88" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K88" s="15">
-        <v>0</v>
-      </c>
-      <c r="L88" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M88" s="19">
-        <v>0</v>
-      </c>
-      <c r="N88" s="15"/>
-      <c r="O88" s="15"/>
-      <c r="P88" s="20">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="15" t="s">
-        <v>361</v>
-      </c>
-      <c r="B89" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="C89" s="16">
-        <v>1800000080</v>
-      </c>
-      <c r="D89" s="17">
-        <v>31048</v>
-      </c>
-      <c r="E89" s="18" t="s">
-        <v>500</v>
-      </c>
-      <c r="F89" s="15"/>
-      <c r="G89" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H89" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="I89" s="15"/>
-      <c r="J89" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="K89" s="15">
-        <v>0</v>
-      </c>
-      <c r="L89" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M89" s="19">
-        <v>240</v>
-      </c>
-      <c r="N89" s="15"/>
-      <c r="O89" s="15" t="s">
-        <v>525</v>
-      </c>
-      <c r="P89" s="20">
+      <c r="N89" s="14">
+        <v>0</v>
+      </c>
+      <c r="O89" s="9">
         <v>44562</v>
       </c>
     </row>

--- a/normalizacion_datos.xlsx
+++ b/normalizacion_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Proyectos\app_agua\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEE9614-11F4-47F8-A29D-C47B8355B1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91AE5B9F-1DFB-43E3-8A7F-B5B941A24084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E2268286-99C0-4F97-A086-55F9B04399C9}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="520">
   <si>
     <t>id</t>
   </si>
@@ -1610,6 +1610,12 @@
   </si>
   <si>
     <t>multas</t>
+  </si>
+  <si>
+    <t>Fernando Francisco</t>
+  </si>
+  <si>
+    <t>deudas_alcantarillado</t>
   </si>
 </sst>
 </file>
@@ -1672,46 +1678,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2202,28 +2200,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C16C49C9-4843-476F-A284-418FFA1EFBFA}">
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.6640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.77734375" style="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="11.5546875" style="6"/>
+    <col min="1" max="1" width="16.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="11.5546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -2245,7 +2244,7 @@
       <c r="G1" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="2" t="s">
         <v>363</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -2260,37 +2259,40 @@
       <c r="L1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="11" t="s">
         <v>366</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="13" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="14" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="9">
         <v>1800000001</v>
       </c>
-      <c r="D2" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="D2" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>397</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="4">
         <v>1208021050</v>
       </c>
       <c r="I2" s="4"/>
@@ -2303,37 +2305,37 @@
       <c r="L2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M2" s="12">
         <v>7.3</v>
       </c>
       <c r="N2" s="4">
         <v>40</v>
       </c>
-      <c r="O2" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O2" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>329</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="9">
         <v>1800000002</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>20090</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>398</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="4">
         <v>1211034239</v>
       </c>
       <c r="I3" s="4"/>
@@ -2346,37 +2348,37 @@
       <c r="L3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="12">
         <v>11.5</v>
       </c>
       <c r="N3" s="4">
         <v>0</v>
       </c>
-      <c r="O3" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O3" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="9">
         <v>1800000003</v>
       </c>
-      <c r="D4" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>399</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="4">
         <v>14511084</v>
       </c>
       <c r="I4" s="4" t="s">
@@ -2391,37 +2393,37 @@
       <c r="L4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="12">
         <v>190.5</v>
       </c>
       <c r="N4" s="4">
         <v>20</v>
       </c>
-      <c r="O4" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O4" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <v>1800000003</v>
       </c>
-      <c r="D5" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>400</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="4">
         <v>8899078</v>
       </c>
       <c r="I5" s="4" t="s">
@@ -2436,37 +2438,37 @@
       <c r="L5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="12">
         <v>483.00000000000006</v>
       </c>
       <c r="N5" s="4">
         <v>20</v>
       </c>
-      <c r="O5" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O5" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="D6" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>401</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="4">
         <v>130628815</v>
       </c>
       <c r="I6" s="4"/>
@@ -2479,37 +2481,37 @@
       <c r="L6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="12">
         <v>0</v>
       </c>
       <c r="N6" s="4">
         <v>25</v>
       </c>
-      <c r="O6" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O6" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <v>1800000005</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>20090</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>402</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="4">
         <v>171430644</v>
       </c>
       <c r="I7" s="4"/>
@@ -2522,37 +2524,37 @@
       <c r="L7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="12">
         <v>20</v>
       </c>
       <c r="N7" s="4">
         <v>25</v>
       </c>
-      <c r="O7" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O7" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <v>1800000006</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>20090</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>403</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="4">
         <v>8896612</v>
       </c>
       <c r="I8" s="4"/>
@@ -2565,37 +2567,37 @@
       <c r="L8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="12">
         <v>59.4</v>
       </c>
       <c r="N8" s="4">
         <v>5</v>
       </c>
-      <c r="O8" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O8" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>487</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="D9" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>404</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="4">
         <v>8896617</v>
       </c>
       <c r="I9" s="4"/>
@@ -2608,37 +2610,37 @@
       <c r="L9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="12">
         <v>27.3</v>
       </c>
       <c r="N9" s="4">
         <v>20</v>
       </c>
-      <c r="O9" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O9" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="9">
         <v>1800000008</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>20090</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>405</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="4">
         <v>12299219</v>
       </c>
       <c r="I10" s="4"/>
@@ -2651,37 +2653,37 @@
       <c r="L10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="12">
         <v>97.200000000000017</v>
       </c>
       <c r="N10" s="4">
         <v>40</v>
       </c>
-      <c r="O10" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O10" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <v>1800000009</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>20090</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>406</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="4">
         <v>8896620</v>
       </c>
       <c r="I11" s="4" t="s">
@@ -2696,37 +2698,37 @@
       <c r="L11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="12">
         <v>0</v>
       </c>
       <c r="N11" s="4">
         <v>25</v>
       </c>
-      <c r="O11" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O11" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="9">
         <v>1800000009</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>20090</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>407</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="4">
         <v>1211034231</v>
       </c>
       <c r="I12" s="4" t="s">
@@ -2741,37 +2743,37 @@
       <c r="L12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="12">
         <v>0</v>
       </c>
       <c r="N12" s="4">
         <v>0</v>
       </c>
-      <c r="O12" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O12" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="9">
         <v>1800000010</v>
       </c>
-      <c r="D13" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E13" s="8" t="s">
+      <c r="D13" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>411</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="4">
         <v>1211033708</v>
       </c>
       <c r="I13" s="4"/>
@@ -2784,37 +2786,37 @@
       <c r="L13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="12">
         <v>14.4</v>
       </c>
       <c r="N13" s="4">
         <v>40</v>
       </c>
-      <c r="O13" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O13" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>59</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="9">
         <v>1800000011</v>
       </c>
-      <c r="D14" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E14" s="8" t="s">
+      <c r="D14" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>409</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="4">
         <v>11817151</v>
       </c>
       <c r="I14" s="4"/>
@@ -2827,37 +2829,37 @@
       <c r="L14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="12">
         <v>55</v>
       </c>
       <c r="N14" s="4">
         <v>40</v>
       </c>
-      <c r="O14" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O14" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>63</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="9">
         <v>1800000012</v>
       </c>
-      <c r="D15" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>412</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="H15" s="4" t="s">
         <v>514</v>
       </c>
       <c r="I15" s="4"/>
@@ -2870,37 +2872,37 @@
       <c r="L15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="12">
         <v>92.5</v>
       </c>
       <c r="N15" s="4">
         <v>20</v>
       </c>
-      <c r="O15" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O15" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>67</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="9">
         <v>1800000013</v>
       </c>
-      <c r="D16" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>408</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="4" t="s">
         <v>491</v>
       </c>
       <c r="I16" s="4"/>
@@ -2913,11 +2915,11 @@
       <c r="L16" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="12">
         <v>26.85</v>
       </c>
       <c r="N16" s="4"/>
-      <c r="O16" s="9">
+      <c r="O16" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -2928,20 +2930,20 @@
       <c r="B17" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="9">
         <v>1800000014</v>
       </c>
-      <c r="D17" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="D17" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>413</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="H17" s="4" t="s">
         <v>515</v>
       </c>
       <c r="I17" s="4"/>
@@ -2954,13 +2956,13 @@
       <c r="L17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M17" s="16">
+      <c r="M17" s="12">
         <v>11.999000000000001</v>
       </c>
       <c r="N17" s="4">
         <v>25</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -2971,20 +2973,20 @@
       <c r="B18" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="9">
         <v>1800000015</v>
       </c>
-      <c r="D18" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>410</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="4">
         <v>1211033520</v>
       </c>
       <c r="I18" s="4"/>
@@ -2997,13 +2999,13 @@
       <c r="L18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="12">
         <v>15.4</v>
       </c>
       <c r="N18" s="4">
         <v>40</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3014,20 +3016,20 @@
       <c r="B19" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="9">
         <v>1800000016</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="6">
         <v>20090</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>414</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="4">
         <v>1211033704</v>
       </c>
       <c r="I19" s="4"/>
@@ -3040,13 +3042,13 @@
       <c r="L19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M19" s="16">
+      <c r="M19" s="12">
         <v>0</v>
       </c>
       <c r="N19" s="4">
         <v>25</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3057,20 +3059,20 @@
       <c r="B20" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="9">
         <v>1800000017</v>
       </c>
-      <c r="D20" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E20" s="8" t="s">
+      <c r="D20" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>415</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="4">
         <v>1211034233</v>
       </c>
       <c r="I20" s="4"/>
@@ -3083,13 +3085,13 @@
       <c r="L20" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="12">
         <v>479.03549999999996</v>
       </c>
       <c r="N20" s="4">
         <v>25</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3100,20 +3102,20 @@
       <c r="B21" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="9">
         <v>1800000017</v>
       </c>
-      <c r="D21" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E21" s="8" t="s">
+      <c r="D21" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>416</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="4">
         <v>21052411</v>
       </c>
       <c r="I21" s="4" t="s">
@@ -3128,11 +3130,11 @@
       <c r="L21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="12">
         <v>594.66150000000005</v>
       </c>
       <c r="N21" s="4"/>
-      <c r="O21" s="9">
+      <c r="O21" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3143,20 +3145,20 @@
       <c r="B22" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="9">
         <v>1800000018</v>
       </c>
-      <c r="D22" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E22" s="8" t="s">
+      <c r="D22" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>417</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="4" t="s">
         <v>516</v>
       </c>
       <c r="I22" s="4"/>
@@ -3169,13 +3171,13 @@
       <c r="L22" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="12">
         <v>85</v>
       </c>
       <c r="N22" s="4">
         <v>40</v>
       </c>
-      <c r="O22" s="9">
+      <c r="O22" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3186,20 +3188,20 @@
       <c r="B23" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="9">
         <v>1800000019</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="6">
         <v>20090</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="7" t="s">
         <v>418</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="4">
         <v>25295328</v>
       </c>
       <c r="I23" s="4" t="s">
@@ -3214,13 +3216,13 @@
       <c r="L23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="16">
+      <c r="M23" s="12">
         <v>257.51660000000004</v>
       </c>
       <c r="N23" s="4">
         <v>20</v>
       </c>
-      <c r="O23" s="9">
+      <c r="O23" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3231,20 +3233,20 @@
       <c r="B24" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="9">
         <v>1800000019</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="6">
         <v>20090</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="7" t="s">
         <v>419</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H24" s="4" t="s">
         <v>516</v>
       </c>
       <c r="I24" s="4" t="s">
@@ -3259,11 +3261,11 @@
       <c r="L24" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M24" s="16">
+      <c r="M24" s="12">
         <v>28</v>
       </c>
       <c r="N24" s="4"/>
-      <c r="O24" s="9">
+      <c r="O24" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3274,20 +3276,20 @@
       <c r="B25" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="9">
         <v>1800000020</v>
       </c>
-      <c r="D25" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E25" s="8" t="s">
+      <c r="D25" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>420</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="4" t="s">
         <v>492</v>
       </c>
       <c r="I25" s="4"/>
@@ -3300,13 +3302,13 @@
       <c r="L25" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="12">
         <v>183.32799999999997</v>
       </c>
       <c r="N25" s="4">
         <v>25</v>
       </c>
-      <c r="O25" s="9">
+      <c r="O25" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3317,20 +3319,20 @@
       <c r="B26" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="9">
         <v>1800000021</v>
       </c>
-      <c r="D26" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E26" s="8" t="s">
+      <c r="D26" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>421</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="4">
         <v>1211033709</v>
       </c>
       <c r="I26" s="4"/>
@@ -3343,13 +3345,13 @@
       <c r="L26" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="12">
         <v>95</v>
       </c>
       <c r="N26" s="4">
         <v>40</v>
       </c>
-      <c r="O26" s="9">
+      <c r="O26" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3360,20 +3362,20 @@
       <c r="B27" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="9">
         <v>1800000022</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>20090</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="7" t="s">
         <v>422</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="4">
         <v>1211033707</v>
       </c>
       <c r="I27" s="4"/>
@@ -3386,13 +3388,13 @@
       <c r="L27" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="12">
         <v>136.4</v>
       </c>
       <c r="N27" s="4">
         <v>40</v>
       </c>
-      <c r="O27" s="9">
+      <c r="O27" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3403,20 +3405,20 @@
       <c r="B28" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="9">
         <v>1800000023</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="6">
         <v>20090</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="7" t="s">
         <v>423</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="4">
         <v>1211034240</v>
       </c>
       <c r="I28" s="4"/>
@@ -3429,13 +3431,13 @@
       <c r="L28" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="12">
         <v>16</v>
       </c>
       <c r="N28" s="4">
         <v>40</v>
       </c>
-      <c r="O28" s="9">
+      <c r="O28" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3446,20 +3448,20 @@
       <c r="B29" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="9">
         <v>1800000024</v>
       </c>
-      <c r="D29" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E29" s="8" t="s">
+      <c r="D29" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>424</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="4">
         <v>1208020366</v>
       </c>
       <c r="I29" s="4"/>
@@ -3472,13 +3474,13 @@
       <c r="L29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="16">
+      <c r="M29" s="12">
         <v>1543.0840000000001</v>
       </c>
       <c r="N29" s="4">
         <v>20</v>
       </c>
-      <c r="O29" s="9">
+      <c r="O29" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3489,20 +3491,20 @@
       <c r="B30" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="9">
         <v>1800000025</v>
       </c>
-      <c r="D30" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E30" s="8" t="s">
+      <c r="D30" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>425</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H30" s="4" t="s">
         <v>493</v>
       </c>
       <c r="I30" s="4"/>
@@ -3515,13 +3517,13 @@
       <c r="L30" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="16">
+      <c r="M30" s="12">
         <v>231.9</v>
       </c>
       <c r="N30" s="4">
         <v>40</v>
       </c>
-      <c r="O30" s="9">
+      <c r="O30" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3532,20 +3534,20 @@
       <c r="B31" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="9">
         <v>1800000026</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="6">
         <v>20090</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="7" t="s">
         <v>426</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="4">
         <v>1211036816</v>
       </c>
       <c r="I31" s="4" t="s">
@@ -3560,13 +3562,13 @@
       <c r="L31" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="12">
         <v>173</v>
       </c>
       <c r="N31" s="4">
         <v>40</v>
       </c>
-      <c r="O31" s="9">
+      <c r="O31" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3577,20 +3579,20 @@
       <c r="B32" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="9">
         <v>1800000026</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="6">
         <v>20090</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="7" t="s">
         <v>427</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H32" s="13">
+      <c r="H32" s="4">
         <v>1211036811</v>
       </c>
       <c r="I32" s="4" t="s">
@@ -3605,11 +3607,11 @@
       <c r="L32" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="12">
         <v>8</v>
       </c>
       <c r="N32" s="4"/>
-      <c r="O32" s="9">
+      <c r="O32" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3620,20 +3622,20 @@
       <c r="B33" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="9">
         <v>1800000027</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="6">
         <v>20090</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="7" t="s">
         <v>428</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H33" s="13">
+      <c r="H33" s="4">
         <v>1211034334</v>
       </c>
       <c r="I33" s="4"/>
@@ -3646,13 +3648,13 @@
       <c r="L33" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="12">
         <v>3</v>
       </c>
       <c r="N33" s="4">
         <v>25</v>
       </c>
-      <c r="O33" s="9">
+      <c r="O33" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3663,20 +3665,20 @@
       <c r="B34" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="9">
         <v>1800000028</v>
       </c>
-      <c r="D34" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E34" s="8" t="s">
+      <c r="D34" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>429</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="H34" s="4" t="s">
         <v>516</v>
       </c>
       <c r="I34" s="4"/>
@@ -3689,13 +3691,13 @@
       <c r="L34" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="12">
         <v>258</v>
       </c>
       <c r="N34" s="4">
         <v>40</v>
       </c>
-      <c r="O34" s="9">
+      <c r="O34" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3706,20 +3708,20 @@
       <c r="B35" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="9">
         <v>1800000029</v>
       </c>
-      <c r="D35" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E35" s="8" t="s">
+      <c r="D35" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>430</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H35" s="13" t="s">
+      <c r="H35" s="4" t="s">
         <v>516</v>
       </c>
       <c r="I35" s="4"/>
@@ -3732,13 +3734,13 @@
       <c r="L35" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M35" s="16">
+      <c r="M35" s="12">
         <v>5</v>
       </c>
       <c r="N35" s="4">
         <v>40</v>
       </c>
-      <c r="O35" s="9">
+      <c r="O35" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3749,20 +3751,20 @@
       <c r="B36" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="9">
         <v>1800000030</v>
       </c>
-      <c r="D36" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E36" s="8" t="s">
+      <c r="D36" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>431</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="H36" s="13" t="s">
+      <c r="H36" s="4" t="s">
         <v>516</v>
       </c>
       <c r="I36" s="4"/>
@@ -3775,13 +3777,13 @@
       <c r="L36" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M36" s="16">
+      <c r="M36" s="12">
         <v>35</v>
       </c>
       <c r="N36" s="4">
         <v>40</v>
       </c>
-      <c r="O36" s="9">
+      <c r="O36" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3792,20 +3794,20 @@
       <c r="B37" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="9">
         <v>1800000031</v>
       </c>
-      <c r="D37" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E37" s="8" t="s">
+      <c r="D37" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>432</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H37" s="13">
+      <c r="H37" s="4">
         <v>1211034238</v>
       </c>
       <c r="I37" s="4"/>
@@ -3818,13 +3820,13 @@
       <c r="L37" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M37" s="16">
+      <c r="M37" s="12">
         <v>45</v>
       </c>
       <c r="N37" s="4">
         <v>5</v>
       </c>
-      <c r="O37" s="9">
+      <c r="O37" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3835,20 +3837,20 @@
       <c r="B38" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="9">
         <v>1800000032</v>
       </c>
-      <c r="D38" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E38" s="8" t="s">
+      <c r="D38" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>433</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H38" s="4">
         <v>1211034232</v>
       </c>
       <c r="I38" s="4"/>
@@ -3861,11 +3863,11 @@
       <c r="L38" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="12">
         <v>75</v>
       </c>
       <c r="N38" s="4"/>
-      <c r="O38" s="9">
+      <c r="O38" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3876,20 +3878,20 @@
       <c r="B39" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="D39" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E39" s="8" t="s">
+      <c r="D39" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E39" s="7" t="s">
         <v>434</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H39" s="4">
         <v>1208020313</v>
       </c>
       <c r="I39" s="4"/>
@@ -3902,11 +3904,11 @@
       <c r="L39" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M39" s="16">
+      <c r="M39" s="12">
         <v>15.6</v>
       </c>
       <c r="N39" s="4"/>
-      <c r="O39" s="9">
+      <c r="O39" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3917,20 +3919,20 @@
       <c r="B40" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="9">
         <v>1800000034</v>
       </c>
-      <c r="D40" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E40" s="8" t="s">
+      <c r="D40" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E40" s="7" t="s">
         <v>435</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H40" s="13">
+      <c r="H40" s="4">
         <v>1208020318</v>
       </c>
       <c r="I40" s="4"/>
@@ -3943,13 +3945,13 @@
       <c r="L40" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M40" s="16">
+      <c r="M40" s="12">
         <v>0</v>
       </c>
       <c r="N40" s="4">
         <v>5</v>
       </c>
-      <c r="O40" s="9">
+      <c r="O40" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -3960,20 +3962,20 @@
       <c r="B41" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="9">
         <v>1800000035</v>
       </c>
-      <c r="D41" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E41" s="8" t="s">
+      <c r="D41" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>436</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H41" s="13">
+      <c r="H41" s="4">
         <v>1208020320</v>
       </c>
       <c r="I41" s="4"/>
@@ -3986,11 +3988,11 @@
       <c r="L41" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M41" s="16">
+      <c r="M41" s="12">
         <v>0</v>
       </c>
       <c r="N41" s="4"/>
-      <c r="O41" s="9">
+      <c r="O41" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -4001,20 +4003,20 @@
       <c r="B42" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="9">
         <v>1800000036</v>
       </c>
-      <c r="D42" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E42" s="8" t="s">
+      <c r="D42" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>437</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H42" s="13">
+      <c r="H42" s="4">
         <v>1208020314</v>
       </c>
       <c r="I42" s="4"/>
@@ -4027,13 +4029,13 @@
       <c r="L42" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="12">
         <v>0</v>
       </c>
       <c r="N42" s="4">
         <v>20</v>
       </c>
-      <c r="O42" s="9">
+      <c r="O42" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -4044,20 +4046,20 @@
       <c r="B43" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="9">
         <v>1800000036</v>
       </c>
-      <c r="D43" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E43" s="8" t="s">
+      <c r="D43" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>438</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H43" s="13">
+      <c r="H43" s="4">
         <v>1208020827</v>
       </c>
       <c r="I43" s="4"/>
@@ -4070,13 +4072,13 @@
       <c r="L43" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="12">
         <v>10</v>
       </c>
       <c r="N43" s="4">
         <v>20</v>
       </c>
-      <c r="O43" s="9">
+      <c r="O43" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -4087,20 +4089,20 @@
       <c r="B44" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="9">
         <v>1800000037</v>
       </c>
-      <c r="D44" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E44" s="8" t="s">
+      <c r="D44" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>439</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H44" s="13">
+      <c r="H44" s="4">
         <v>1208020315</v>
       </c>
       <c r="I44" s="4"/>
@@ -4113,11 +4115,11 @@
       <c r="L44" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M44" s="16">
+      <c r="M44" s="12">
         <v>5</v>
       </c>
       <c r="N44" s="4"/>
-      <c r="O44" s="9">
+      <c r="O44" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -4128,20 +4130,20 @@
       <c r="B45" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="9">
         <v>1800000038</v>
       </c>
-      <c r="D45" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E45" s="8" t="s">
+      <c r="D45" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>440</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H45" s="13">
+      <c r="H45" s="4">
         <v>1208020317</v>
       </c>
       <c r="I45" s="4"/>
@@ -4154,11 +4156,11 @@
       <c r="L45" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M45" s="16">
+      <c r="M45" s="12">
         <v>0</v>
       </c>
       <c r="N45" s="4"/>
-      <c r="O45" s="9">
+      <c r="O45" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -4169,20 +4171,20 @@
       <c r="B46" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="9">
         <v>1800000039</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="6">
         <v>20090</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="7" t="s">
         <v>441</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H46" s="13">
+      <c r="H46" s="4">
         <v>1208020311</v>
       </c>
       <c r="I46" s="4" t="s">
@@ -4197,11 +4199,11 @@
       <c r="L46" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M46" s="16">
+      <c r="M46" s="12">
         <v>0</v>
       </c>
       <c r="N46" s="4"/>
-      <c r="O46" s="9">
+      <c r="O46" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -4212,20 +4214,20 @@
       <c r="B47" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="9">
         <v>1800000039</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="6">
         <v>20090</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="7" t="s">
         <v>442</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H47" s="13">
+      <c r="H47" s="4">
         <v>1208020368</v>
       </c>
       <c r="I47" s="4" t="s">
@@ -4240,11 +4242,11 @@
       <c r="L47" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M47" s="16">
+      <c r="M47" s="12">
         <v>0</v>
       </c>
       <c r="N47" s="4"/>
-      <c r="O47" s="9">
+      <c r="O47" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -4255,20 +4257,20 @@
       <c r="B48" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="9">
         <v>1800000040</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="6">
         <v>20090</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="7" t="s">
         <v>443</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H48" s="13">
+      <c r="H48" s="4">
         <v>1208020826</v>
       </c>
       <c r="I48" s="4"/>
@@ -4281,35 +4283,35 @@
       <c r="L48" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M48" s="16">
+      <c r="M48" s="12">
         <v>0</v>
       </c>
       <c r="N48" s="4"/>
-      <c r="O48" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O48" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>180</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="9">
         <v>1800000041</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D49" s="6">
         <v>20090</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="7" t="s">
         <v>444</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H49" s="13">
+      <c r="H49" s="4">
         <v>1208020319</v>
       </c>
       <c r="I49" s="4"/>
@@ -4322,35 +4324,35 @@
       <c r="L49" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M49" s="16">
+      <c r="M49" s="12">
         <v>0</v>
       </c>
       <c r="N49" s="4"/>
-      <c r="O49" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O49" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>498</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="6">
         <v>20090</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="7" t="s">
         <v>445</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H50" s="13">
+      <c r="H50" s="4">
         <v>1208020828</v>
       </c>
       <c r="I50" s="4"/>
@@ -4363,35 +4365,35 @@
       <c r="L50" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M50" s="16">
+      <c r="M50" s="12">
         <v>0</v>
       </c>
       <c r="N50" s="4"/>
-      <c r="O50" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O50" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>502</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="D51" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E51" s="8" t="s">
+      <c r="D51" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>446</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H51" s="13">
+      <c r="H51" s="4">
         <v>1208020369</v>
       </c>
       <c r="I51" s="4"/>
@@ -4404,37 +4406,37 @@
       <c r="L51" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M51" s="16">
+      <c r="M51" s="12">
         <v>92.5</v>
       </c>
       <c r="N51" s="4">
         <v>40</v>
       </c>
-      <c r="O51" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O51" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>506</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="D52" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E52" s="8" t="s">
+      <c r="D52" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>447</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H52" s="13" t="s">
+      <c r="H52" s="4" t="s">
         <v>504</v>
       </c>
       <c r="I52" s="4"/>
@@ -4447,37 +4449,37 @@
       <c r="L52" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M52" s="16">
+      <c r="M52" s="12">
         <v>0</v>
       </c>
       <c r="N52" s="4">
         <v>5</v>
       </c>
-      <c r="O52" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O52" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>197</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="9">
         <v>1800000045</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="6">
         <v>20090</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="7" t="s">
         <v>448</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H53" s="13">
+      <c r="H53" s="4">
         <v>1603004786</v>
       </c>
       <c r="I53" s="4"/>
@@ -4490,35 +4492,35 @@
       <c r="L53" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M53" s="16">
+      <c r="M53" s="12">
         <v>8</v>
       </c>
       <c r="N53" s="4"/>
-      <c r="O53" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O53" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>201</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="9">
         <v>1800000046</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="6">
         <v>20090</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="7" t="s">
         <v>449</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H54" s="13">
+      <c r="H54" s="4">
         <v>1208020824</v>
       </c>
       <c r="I54" s="4"/>
@@ -4531,35 +4533,35 @@
       <c r="L54" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M54" s="16">
+      <c r="M54" s="12">
         <v>2</v>
       </c>
       <c r="N54" s="4"/>
-      <c r="O54" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O54" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>205</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="9">
         <v>1800000047</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="6">
         <v>20090</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="7" t="s">
         <v>450</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H55" s="13">
+      <c r="H55" s="4">
         <v>1208020830</v>
       </c>
       <c r="I55" s="4"/>
@@ -4572,37 +4574,37 @@
       <c r="L55" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M55" s="16">
+      <c r="M55" s="12">
         <v>4</v>
       </c>
       <c r="N55" s="4">
         <v>40</v>
       </c>
-      <c r="O55" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O55" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>209</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="9">
         <v>1800000048</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="6">
         <v>20090</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="7" t="s">
         <v>451</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H56" s="13">
+      <c r="H56" s="4">
         <v>1211034237</v>
       </c>
       <c r="I56" s="4"/>
@@ -4615,42 +4617,42 @@
       <c r="L56" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M56" s="16">
+      <c r="M56" s="12">
         <v>4</v>
       </c>
       <c r="N56" s="4">
         <v>5</v>
       </c>
-      <c r="O56" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O56" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>214</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="9">
         <v>1800000049</v>
       </c>
-      <c r="D57" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E57" s="8" t="s">
+      <c r="D57" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>452</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H57" s="13">
+      <c r="H57" s="4">
         <v>1208020821</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K57" s="4">
         <v>4277</v>
@@ -4658,42 +4660,45 @@
       <c r="L57" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M57" s="16">
+      <c r="M57" s="12">
         <v>0</v>
       </c>
       <c r="N57" s="4">
         <v>40</v>
       </c>
-      <c r="O57" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O57" s="1">
+        <v>44562</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>218</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="9">
         <v>1800000050</v>
       </c>
-      <c r="D58" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E58" s="8" t="s">
+      <c r="D58" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E58" s="7" t="s">
         <v>453</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H58" s="13">
+      <c r="H58" s="4">
         <v>1208020822</v>
       </c>
       <c r="I58" s="4"/>
       <c r="J58" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K58" s="4">
         <v>2242</v>
@@ -4701,40 +4706,43 @@
       <c r="L58" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M58" s="16">
+      <c r="M58" s="12">
         <v>0</v>
       </c>
       <c r="N58" s="4"/>
-      <c r="O58" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O58" s="1">
+        <v>44562</v>
+      </c>
+      <c r="P58" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>508</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="D59" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E59" s="8" t="s">
+      <c r="D59" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>454</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H59" s="13">
+      <c r="H59" s="4">
         <v>1208020823</v>
       </c>
       <c r="I59" s="4"/>
       <c r="J59" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K59" s="4">
         <v>767</v>
@@ -4742,42 +4750,45 @@
       <c r="L59" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M59" s="16">
+      <c r="M59" s="12">
         <v>0</v>
       </c>
       <c r="N59" s="4">
         <v>5</v>
       </c>
-      <c r="O59" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O59" s="1">
+        <v>44562</v>
+      </c>
+      <c r="P59" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>509</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="D60" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E60" s="8" t="s">
+      <c r="D60" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E60" s="7" t="s">
         <v>455</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H60" s="13">
+      <c r="H60" s="4">
         <v>1211034236</v>
       </c>
       <c r="I60" s="4"/>
       <c r="J60" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K60" s="4">
         <v>2991</v>
@@ -4785,40 +4796,43 @@
       <c r="L60" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M60" s="16">
+      <c r="M60" s="12">
         <v>0</v>
       </c>
       <c r="N60" s="4"/>
-      <c r="O60" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O60" s="1">
+        <v>44562</v>
+      </c>
+      <c r="P60" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="9">
         <v>1800000053</v>
       </c>
-      <c r="D61" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E61" s="8" t="s">
+      <c r="D61" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>456</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H61" s="13">
+      <c r="H61" s="4">
         <v>1208020312</v>
       </c>
       <c r="I61" s="4"/>
       <c r="J61" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K61" s="4">
         <v>4233</v>
@@ -4826,42 +4840,45 @@
       <c r="L61" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M61" s="16">
+      <c r="M61" s="12">
         <v>51.8</v>
       </c>
       <c r="N61" s="4">
         <v>20</v>
       </c>
-      <c r="O61" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O61" s="1">
+        <v>44562</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>79</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C62" s="11">
+      <c r="C62" s="9">
         <v>1800000054</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="6">
         <v>20090</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="7" t="s">
         <v>457</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H62" s="13">
+      <c r="H62" s="4">
         <v>1203020825</v>
       </c>
       <c r="I62" s="4"/>
       <c r="J62" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K62" s="4">
         <v>6575</v>
@@ -4869,42 +4886,45 @@
       <c r="L62" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M62" s="16">
+      <c r="M62" s="12">
         <v>0</v>
       </c>
       <c r="N62" s="4">
         <v>20</v>
       </c>
-      <c r="O62" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O62" s="1">
+        <v>44562</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>236</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="9">
         <v>1800000055</v>
       </c>
-      <c r="D63" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E63" s="8" t="s">
+      <c r="D63" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E63" s="7" t="s">
         <v>458</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H63" s="13">
+      <c r="H63" s="4">
         <v>1208021044</v>
       </c>
       <c r="I63" s="4"/>
       <c r="J63" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K63" s="4">
         <v>2384</v>
@@ -4912,42 +4932,45 @@
       <c r="L63" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M63" s="16">
+      <c r="M63" s="12">
         <v>15</v>
       </c>
       <c r="N63" s="4">
         <v>20</v>
       </c>
-      <c r="O63" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O63" s="1">
+        <v>44562</v>
+      </c>
+      <c r="P63" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>240</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="C64" s="11">
+      <c r="C64" s="9">
         <v>1800000056</v>
       </c>
-      <c r="D64" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E64" s="8" t="s">
+      <c r="D64" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>459</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H64" s="13">
+      <c r="H64" s="4">
         <v>1208021048</v>
       </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K64" s="4">
         <v>4975</v>
@@ -4955,40 +4978,43 @@
       <c r="L64" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M64" s="16">
+      <c r="M64" s="12">
         <v>11.1</v>
       </c>
       <c r="N64" s="4"/>
-      <c r="O64" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O64" s="1">
+        <v>44562</v>
+      </c>
+      <c r="P64" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>244</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="9">
         <v>1800000057</v>
       </c>
-      <c r="D65" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E65" s="8" t="s">
+      <c r="D65" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E65" s="7" t="s">
         <v>460</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H65" s="13">
+      <c r="H65" s="4">
         <v>1208021047</v>
       </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K65" s="4">
         <v>4070</v>
@@ -4996,37 +5022,40 @@
       <c r="L65" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M65" s="16">
+      <c r="M65" s="12">
         <v>51.5</v>
       </c>
       <c r="N65" s="4">
         <v>40</v>
       </c>
-      <c r="O65" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O65" s="1">
+        <v>44562</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>244</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="C66" s="11">
+      <c r="C66" s="9">
         <v>1800000058</v>
       </c>
-      <c r="D66" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E66" s="8" t="s">
+      <c r="D66" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E66" s="7" t="s">
         <v>461</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H66" s="13">
+      <c r="H66" s="4">
         <v>1208020829</v>
       </c>
       <c r="I66" s="4"/>
@@ -5039,42 +5068,42 @@
       <c r="L66" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M66" s="16">
+      <c r="M66" s="12">
         <v>0</v>
       </c>
       <c r="N66" s="4"/>
-      <c r="O66" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O66" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>251</v>
+        <v>518</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="9">
         <v>1800000059</v>
       </c>
-      <c r="D67" s="7">
+      <c r="D67" s="6">
         <v>20090</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="7" t="s">
         <v>462</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H67" s="13">
+      <c r="H67" s="4">
         <v>1208020362</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>485</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K67" s="4">
         <v>5998</v>
@@ -5082,35 +5111,35 @@
       <c r="L67" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M67" s="16">
+      <c r="M67" s="12">
         <v>0</v>
       </c>
       <c r="N67" s="4"/>
-      <c r="O67" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O67" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>251</v>
+        <v>518</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="9">
         <v>1800000059</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D68" s="6">
         <v>20090</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="7" t="s">
         <v>463</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H68" s="13" t="s">
+      <c r="H68" s="4" t="s">
         <v>516</v>
       </c>
       <c r="I68" s="4" t="s">
@@ -5125,35 +5154,35 @@
       <c r="L68" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M68" s="16">
+      <c r="M68" s="12">
         <v>8</v>
       </c>
       <c r="N68" s="4"/>
-      <c r="O68" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O68" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>255</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="9">
         <v>1800000060</v>
       </c>
-      <c r="D69" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E69" s="8" t="s">
+      <c r="D69" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E69" s="7" t="s">
         <v>464</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H69" s="13">
+      <c r="H69" s="4">
         <v>1208020365</v>
       </c>
       <c r="I69" s="4"/>
@@ -5166,37 +5195,37 @@
       <c r="L69" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M69" s="16">
+      <c r="M69" s="12">
         <v>5</v>
       </c>
       <c r="N69" s="4">
         <v>40</v>
       </c>
-      <c r="O69" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O69" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>259</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="9">
         <v>1800000061</v>
       </c>
-      <c r="D70" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E70" s="8" t="s">
+      <c r="D70" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E70" s="7" t="s">
         <v>465</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H70" s="13">
+      <c r="H70" s="4">
         <v>8899276</v>
       </c>
       <c r="I70" s="4"/>
@@ -5209,35 +5238,35 @@
       <c r="L70" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M70" s="16">
+      <c r="M70" s="12">
         <v>0</v>
       </c>
       <c r="N70" s="4"/>
-      <c r="O70" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O70" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>240</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="9">
         <v>1800000062</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="6">
         <v>20090</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="7" t="s">
         <v>466</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H71" s="13">
+      <c r="H71" s="4">
         <v>14511085</v>
       </c>
       <c r="I71" s="4"/>
@@ -5250,42 +5279,43 @@
       <c r="L71" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M71" s="16">
+      <c r="M71" s="12">
         <v>8</v>
       </c>
       <c r="N71" s="4">
         <v>5</v>
       </c>
-      <c r="O71" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O71" s="1">
+        <v>44562</v>
+      </c>
+      <c r="P71" s="4"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>266</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C72" s="11">
+      <c r="C72" s="9">
         <v>1800000063</v>
       </c>
-      <c r="D72" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E72" s="8" t="s">
+      <c r="D72" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E72" s="7" t="s">
         <v>467</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H72" s="13" t="s">
+      <c r="H72" s="4" t="s">
         <v>512</v>
       </c>
       <c r="I72" s="4"/>
       <c r="J72" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K72" s="4">
         <v>780.45</v>
@@ -5293,35 +5323,38 @@
       <c r="L72" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M72" s="16">
+      <c r="M72" s="12">
         <v>0</v>
       </c>
       <c r="N72" s="4"/>
-      <c r="O72" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O72" s="1">
+        <v>44562</v>
+      </c>
+      <c r="P72" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>205</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C73" s="11">
+      <c r="C73" s="9">
         <v>1800000064</v>
       </c>
-      <c r="D73" s="7">
+      <c r="D73" s="6">
         <v>20090</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="7" t="s">
         <v>468</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H73" s="13">
+      <c r="H73" s="4">
         <v>1208020367</v>
       </c>
       <c r="I73" s="4"/>
@@ -5334,37 +5367,37 @@
       <c r="L73" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M73" s="16">
+      <c r="M73" s="12">
         <v>129.80000000000001</v>
       </c>
       <c r="N73" s="4">
         <v>20</v>
       </c>
-      <c r="O73" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O73" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C74" s="11">
+      <c r="C74" s="9">
         <v>1800000065</v>
       </c>
-      <c r="D74" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E74" s="8" t="s">
+      <c r="D74" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E74" s="7" t="s">
         <v>469</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H74" s="13">
+      <c r="H74" s="4">
         <v>1208022066</v>
       </c>
       <c r="I74" s="4"/>
@@ -5377,37 +5410,37 @@
       <c r="L74" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M74" s="16">
+      <c r="M74" s="12">
         <v>2.8</v>
       </c>
       <c r="N74" s="4">
         <v>20</v>
       </c>
-      <c r="O74" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O74" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>277</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="C75" s="11">
+      <c r="C75" s="9">
         <v>1800000066</v>
       </c>
-      <c r="D75" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E75" s="8" t="s">
+      <c r="D75" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E75" s="7" t="s">
         <v>470</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H75" s="13">
+      <c r="H75" s="4">
         <v>1208021049</v>
       </c>
       <c r="I75" s="4"/>
@@ -5420,35 +5453,35 @@
       <c r="L75" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M75" s="16">
+      <c r="M75" s="12">
         <v>50.8</v>
       </c>
       <c r="N75" s="4"/>
-      <c r="O75" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O75" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>281</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="C76" s="11">
+      <c r="C76" s="9">
         <v>1800000067</v>
       </c>
-      <c r="D76" s="7">
+      <c r="D76" s="6">
         <v>20090</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="E76" s="7" t="s">
         <v>471</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H76" s="13">
+      <c r="H76" s="4">
         <v>1208022061</v>
       </c>
       <c r="I76" s="4"/>
@@ -5461,37 +5494,37 @@
       <c r="L76" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M76" s="16">
+      <c r="M76" s="12">
         <v>0</v>
       </c>
       <c r="N76" s="4">
         <v>20</v>
       </c>
-      <c r="O76" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O76" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>285</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="C77" s="11">
+      <c r="C77" s="9">
         <v>1800000068</v>
       </c>
-      <c r="D77" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E77" s="8" t="s">
+      <c r="D77" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E77" s="7" t="s">
         <v>472</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H77" s="13">
+      <c r="H77" s="4">
         <v>1208021046</v>
       </c>
       <c r="I77" s="4"/>
@@ -5504,35 +5537,35 @@
       <c r="L77" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M77" s="16">
+      <c r="M77" s="12">
         <v>0</v>
       </c>
       <c r="N77" s="4"/>
-      <c r="O77" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O77" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>92</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C78" s="11">
+      <c r="C78" s="9">
         <v>1800000069</v>
       </c>
-      <c r="D78" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E78" s="8" t="s">
+      <c r="D78" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E78" s="7" t="s">
         <v>473</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H78" s="13">
+      <c r="H78" s="4">
         <v>1208020363</v>
       </c>
       <c r="I78" s="4"/>
@@ -5545,35 +5578,35 @@
       <c r="L78" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M78" s="16">
+      <c r="M78" s="12">
         <v>0</v>
       </c>
       <c r="N78" s="4"/>
-      <c r="O78" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O78" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>293</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="9">
         <v>1800000070</v>
       </c>
-      <c r="D79" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E79" s="8" t="s">
+      <c r="D79" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E79" s="7" t="s">
         <v>474</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H79" s="13">
+      <c r="H79" s="4">
         <v>1208020364</v>
       </c>
       <c r="I79" s="4"/>
@@ -5586,37 +5619,37 @@
       <c r="L79" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M79" s="16">
+      <c r="M79" s="12">
         <v>0</v>
       </c>
       <c r="N79" s="4">
         <v>5</v>
       </c>
-      <c r="O79" s="9">
-        <v>44562</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O79" s="1">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>297</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="C80" s="11">
+      <c r="C80" s="9">
         <v>1800000071</v>
       </c>
-      <c r="D80" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E80" s="8" t="s">
+      <c r="D80" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E80" s="7" t="s">
         <v>475</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H80" s="13">
+      <c r="H80" s="4">
         <v>2540886190</v>
       </c>
       <c r="I80" s="4"/>
@@ -5629,13 +5662,13 @@
       <c r="L80" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M80" s="16">
+      <c r="M80" s="12">
         <v>124.7</v>
       </c>
       <c r="N80" s="4">
         <v>20</v>
       </c>
-      <c r="O80" s="9">
+      <c r="O80" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -5646,20 +5679,20 @@
       <c r="B81" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C81" s="11">
+      <c r="C81" s="9">
         <v>1800000072</v>
       </c>
-      <c r="D81" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E81" s="8" t="s">
+      <c r="D81" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E81" s="7" t="s">
         <v>476</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H81" s="13">
+      <c r="H81" s="4">
         <v>1208021041</v>
       </c>
       <c r="I81" s="4"/>
@@ -5672,13 +5705,13 @@
       <c r="L81" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M81" s="16">
+      <c r="M81" s="12">
         <v>5</v>
       </c>
       <c r="N81" s="4">
         <v>20</v>
       </c>
-      <c r="O81" s="9">
+      <c r="O81" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -5689,20 +5722,20 @@
       <c r="B82" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C82" s="11">
+      <c r="C82" s="9">
         <v>1800000073</v>
       </c>
-      <c r="D82" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E82" s="8" t="s">
+      <c r="D82" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E82" s="7" t="s">
         <v>477</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H82" s="13">
+      <c r="H82" s="4">
         <v>1208021045</v>
       </c>
       <c r="I82" s="4"/>
@@ -5715,11 +5748,11 @@
       <c r="L82" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M82" s="16">
+      <c r="M82" s="12">
         <v>15</v>
       </c>
       <c r="N82" s="4"/>
-      <c r="O82" s="9">
+      <c r="O82" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -5730,20 +5763,20 @@
       <c r="B83" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="9">
         <v>1800000074</v>
       </c>
-      <c r="D83" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E83" s="8" t="s">
+      <c r="D83" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E83" s="7" t="s">
         <v>478</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H83" s="13">
+      <c r="H83" s="4">
         <v>1208021043</v>
       </c>
       <c r="I83" s="4"/>
@@ -5756,13 +5789,13 @@
       <c r="L83" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M83" s="16">
+      <c r="M83" s="12">
         <v>182.3</v>
       </c>
       <c r="N83" s="4">
         <v>40</v>
       </c>
-      <c r="O83" s="9">
+      <c r="O83" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -5773,20 +5806,20 @@
       <c r="B84" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="C84" s="11">
+      <c r="C84" s="9">
         <v>1800000075</v>
       </c>
-      <c r="D84" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E84" s="8" t="s">
+      <c r="D84" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E84" s="7" t="s">
         <v>479</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H84" s="13">
+      <c r="H84" s="4">
         <v>1208022062</v>
       </c>
       <c r="I84" s="4"/>
@@ -5799,11 +5832,11 @@
       <c r="L84" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M84" s="16">
+      <c r="M84" s="12">
         <v>0</v>
       </c>
       <c r="N84" s="4"/>
-      <c r="O84" s="9">
+      <c r="O84" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -5814,20 +5847,20 @@
       <c r="B85" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="9">
         <v>1800000076</v>
       </c>
-      <c r="D85" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E85" s="8" t="s">
+      <c r="D85" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E85" s="7" t="s">
         <v>480</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H85" s="13">
+      <c r="H85" s="4">
         <v>1208022063</v>
       </c>
       <c r="I85" s="4"/>
@@ -5840,11 +5873,11 @@
       <c r="L85" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M85" s="16">
+      <c r="M85" s="12">
         <v>0</v>
       </c>
       <c r="N85" s="4"/>
-      <c r="O85" s="9">
+      <c r="O85" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -5855,20 +5888,20 @@
       <c r="B86" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="C86" s="11">
+      <c r="C86" s="9">
         <v>1800000077</v>
       </c>
-      <c r="D86" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E86" s="8" t="s">
+      <c r="D86" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E86" s="7" t="s">
         <v>481</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H86" s="13">
+      <c r="H86" s="4">
         <v>1208020844</v>
       </c>
       <c r="I86" s="4"/>
@@ -5881,10 +5914,10 @@
       <c r="L86" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M86" s="16">
+      <c r="M86" s="12">
         <v>40</v>
       </c>
-      <c r="O86" s="10">
+      <c r="O86" s="8">
         <v>44562</v>
       </c>
     </row>
@@ -5895,20 +5928,20 @@
       <c r="B87" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="9">
         <v>1800000078</v>
       </c>
-      <c r="D87" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E87" s="8" t="s">
+      <c r="D87" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E87" s="7" t="s">
         <v>482</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H87" s="13">
+      <c r="H87" s="4">
         <v>1208020370</v>
       </c>
       <c r="I87" s="4"/>
@@ -5921,13 +5954,13 @@
       <c r="L87" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M87" s="14">
+      <c r="M87" s="10">
         <v>180.39999999999998</v>
       </c>
-      <c r="N87" s="14">
+      <c r="N87" s="10">
         <v>40</v>
       </c>
-      <c r="O87" s="9">
+      <c r="O87" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -5938,20 +5971,20 @@
       <c r="B88" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C88" s="11">
+      <c r="C88" s="9">
         <v>1800000079</v>
       </c>
-      <c r="D88" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E88" s="8" t="s">
+      <c r="D88" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E88" s="7" t="s">
         <v>483</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H88" s="13" t="s">
+      <c r="H88" s="4" t="s">
         <v>516</v>
       </c>
       <c r="I88" s="4"/>
@@ -5964,13 +5997,13 @@
       <c r="L88" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M88" s="14">
-        <v>0</v>
-      </c>
-      <c r="N88" s="14">
+      <c r="M88" s="10">
+        <v>0</v>
+      </c>
+      <c r="N88" s="10">
         <v>40</v>
       </c>
-      <c r="O88" s="9">
+      <c r="O88" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -5981,20 +6014,20 @@
       <c r="B89" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="9">
         <v>1800000080</v>
       </c>
-      <c r="D89" s="7">
-        <v>31048</v>
-      </c>
-      <c r="E89" s="8" t="s">
+      <c r="D89" s="6">
+        <v>31048</v>
+      </c>
+      <c r="E89" s="7" t="s">
         <v>484</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H89" s="13" t="s">
+      <c r="H89" s="4" t="s">
         <v>516</v>
       </c>
       <c r="I89" s="4"/>
@@ -6007,13 +6040,13 @@
       <c r="L89" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M89" s="14">
+      <c r="M89" s="10">
         <v>240</v>
       </c>
-      <c r="N89" s="14">
-        <v>0</v>
-      </c>
-      <c r="O89" s="9">
+      <c r="N89" s="10">
+        <v>0</v>
+      </c>
+      <c r="O89" s="1">
         <v>44562</v>
       </c>
     </row>
